--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -1152,7 +1152,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-03 15:04</t>
+          <t>2026-10-03 16:23</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-03 15:04</t>
+          <t>2026-10-03 16:23</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04T01:35:43.798695</t>
+          <t>2026-10-04T02:19:55.003435</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T01:35:43.800454</t>
+          <t>2026-10-04T02:19:55.013919</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04T01:35:43.800507</t>
+          <t>2026-10-04T02:19:55.013967</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1081,13 +1081,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="33" customWidth="1" min="6" max="6"/>
     <col width="31" customWidth="1" min="7" max="7"/>
@@ -1193,6 +1193,80 @@
       <c r="G3" s="4" t="inlineStr">
         <is>
           <t>2026-10-03T12:53:51.355075Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>gpost_1791059198445</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T02:17:30.097132</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>gpost_1791060565573</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04T02:19:27.070580</t>
         </is>
       </c>
     </row>

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04T02:19:55.003435</t>
+          <t>2026-10-04T17:12:26.504472</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T02:19:55.013919</t>
+          <t>2026-10-04T17:12:26.505543</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04T02:19:55.013967</t>
+          <t>2026-10-04T17:12:26.505567</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1267,6 +1267,43 @@
       <c r="G5" s="4" t="inlineStr">
         <is>
           <t>2026-10-04T02:19:27.070580</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1791114120487</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 4 Oct]</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T17:12:01.861294</t>
         </is>
       </c>
     </row>

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04T17:12:26.504472</t>
+          <t>2026-10-04T21:28:33.140662</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T17:12:26.505543</t>
+          <t>2026-10-04T21:28:33.141546</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04T17:12:26.505567</t>
+          <t>2026-10-04T21:28:33.141566</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04T21:28:33.140662</t>
+          <t>2026-10-04T21:47:52.748597</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T21:28:33.141546</t>
+          <t>2026-10-04T21:47:52.749766</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04T21:28:33.141566</t>
+          <t>2026-10-04T21:47:52.749825</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04T21:47:52.748597</t>
+          <t>2026-10-04T23:54:41.403727</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T21:47:52.749766</t>
+          <t>2026-10-04T23:54:41.414936</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04T21:47:52.749825</t>
+          <t>2026-10-04T23:54:41.415045</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1008,18 +1008,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -1066,6 +1066,47 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Created At</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>rev_1791138036022</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Valued Client</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T23:54:41.423218</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Auto-Replied &amp; Live on Google Maps</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Thank you so much, Ramesh, for your kind 5-star review! The team at Dashmesh Properties is delighted to hear that your experience regarding rental flat and agreement consultation in Pale Gaon, Ambernath East was seamless and rewarding. Providing hassle-free rental agreements and verified landlord verification is always our top priority. We look forward to assisting you, your family, and friends with all future property consultations in Ambernath!</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T23:53:35.623687</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1304,6 +1345,80 @@
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2026-10-04T17:12:01.861294</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1791138036088</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 4 Oct]</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04T23:53:35.632790</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1791138220013</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 4 Oct]</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-04T23:53:41.416765</t>
         </is>
       </c>
     </row>

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -776,20 +776,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04T23:54:41.403727</t>
+          <t>2026-10-07T17:10:12.707264</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:54:41.414936</t>
+          <t>2026-10-07T17:10:12.707288</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,12 +987,208 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04T23:54:41.415045</t>
+          <t>2026-10-07T17:10:12.707311</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2026-10-03T09:30:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>+91 98200 12345</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Ramesh ji</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>New Inquiry</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Rent Agreement (₹1750/side)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Ambernath East</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Hindi / English</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Inquiry</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07T17:10:12.707231</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05T22:56:47.175606</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>9820000001</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Ramesh ji</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>New Inquiry</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Rent Agreement (₹1750/side)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Ambernath East</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Hindi / English</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Inquiry</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T17:10:12.707201</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T23:08:31.949784</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>+919820111222</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Test Client</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>New Inquiry</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Rent Agreement (₹1750/side)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Ambernath East</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>hinglish</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Inquiry</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07T17:10:12.706363</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05T23:08:40.153001</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>+919820555666</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Suresh ji</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>New Inquiry</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Rent Agreement (₹1750/side)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Ambernath East</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>hinglish</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Inquiry</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T17:10:12.704139</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T23:31:45.446077</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1287,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04T23:54:41.423218</t>
+          <t>2026-10-07T17:10:14.320975</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1122,7 +1318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1190,7 +1386,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1223,7 +1419,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -1260,7 +1456,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1297,7 +1493,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -1334,7 +1530,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1371,7 +1567,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1408,7 +1604,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1419,6 +1615,154 @@
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2026-10-04T23:53:41.416765</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1791160896497</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>1 BHK &amp; 2 BHK Affordable Luxury Flats in Pale Gaon, Ambernath East [AI Verified: 5 Oct]</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Discover verified ready-to-move and under-construction flats starting ₹19.5 Lakhs in prime Pale Gaon and Shiv Mandir Road. SBI &amp; HDFC pre-approved up to 90% loan, KDMC water, 5 mins from Ambernath East station. Zero brokerage deals available directly via Dashmesh Properties.</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05T07:10:08.334890</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1791223264554</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 5 Oct]</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05T23:31:06.168821</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1791254438531</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 6 Oct]</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06T08:10:42.848405</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1791351907178</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>1 BHK &amp; 2 BHK Affordable Luxury Flats in Pale Gaon, Ambernath East [AI Verified: 7 Oct]</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Discover verified ready-to-move and under-construction flats starting ₹19.5 Lakhs in prime Pale Gaon and Shiv Mandir Road. SBI &amp; HDFC pre-approved up to 90% loan, KDMC water, 5 mins from Ambernath East station. Zero brokerage deals available directly via Dashmesh Properties.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07T11:16:24.326744</t>
         </is>
       </c>
     </row>

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -776,20 +776,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T17:10:12.707264</t>
+          <t>2026-10-08T10:50:20.911439</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07T17:10:12.707288</t>
+          <t>2026-10-08T10:50:20.915283</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,208 +987,12 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T17:10:12.707311</t>
+          <t>2026-10-08T10:50:20.915350</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2026-10-03T09:30:00.000Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>+91 98200 12345</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Ramesh ji</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>New Inquiry</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Rent Agreement (₹1750/side)</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Ambernath East</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Hindi / English</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>Inquiry</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr"/>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-07T17:10:12.707231</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-05T22:56:47.175606</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>9820000001</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Ramesh ji</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>New Inquiry</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Rent Agreement (₹1750/side)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Ambernath East</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Hindi / English</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Inquiry</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-07T17:10:12.707201</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-05T23:08:31.949784</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>+919820111222</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Test Client</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>New Inquiry</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Rent Agreement (₹1750/side)</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Ambernath East</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>hinglish</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>Inquiry</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr"/>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-07T17:10:12.706363</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-05T23:08:40.153001</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>+919820555666</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Suresh ji</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>New Inquiry</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Rent Agreement (₹1750/side)</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Ambernath East</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>hinglish</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Inquiry</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-07T17:10:12.704139</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-05T23:31:45.446077</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1091,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T17:10:14.320975</t>
+          <t>2026-10-08T10:50:20.925538</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1386,7 +1190,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1419,7 +1223,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -1473,12 +1277,12 @@
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>gpost_1791060565573</t>
+          <t>aipost_1791114120487</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric)</t>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 4 Oct]</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1498,29 +1302,29 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>Published (AI Autonomous)</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T02:19:27.070580</t>
+          <t>2026-10-04T17:12:01.861294</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>aipost_1791114120487</t>
+          <t>aipost_1791160896497</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 4 Oct]</t>
+          <t>1 BHK &amp; 2 BHK Affordable Luxury Flats in Pale Gaon, Ambernath East [AI Verified: 5 Oct]</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+          <t>Discover verified ready-to-move and under-construction flats starting ₹19.5 Lakhs in prime Pale Gaon and Shiv Mandir Road. SBI &amp; HDFC pre-approved up to 90% loan, KDMC water, 5 mins from Ambernath East station. Zero brokerage deals available directly via Dashmesh Properties.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1530,7 +1334,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1540,19 +1344,19 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04T17:12:01.861294</t>
+          <t>2026-10-05T07:10:08.334890</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>aipost_1791138036088</t>
+          <t>aipost_1791223264554</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 4 Oct]</t>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 5 Oct]</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1567,7 +1371,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1577,19 +1381,19 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-04T23:53:35.632790</t>
+          <t>2026-10-05T23:31:06.168821</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>aipost_1791138220013</t>
+          <t>aipost_1791254438531</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 4 Oct]</t>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 6 Oct]</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1604,7 +1408,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1614,19 +1418,19 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-04T23:53:41.416765</t>
+          <t>2026-10-06T08:10:42.848405</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>aipost_1791160896497</t>
+          <t>aipost_1791351907178</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>1 BHK &amp; 2 BHK Affordable Luxury Flats in Pale Gaon, Ambernath East [AI Verified: 5 Oct]</t>
+          <t>1 BHK &amp; 2 BHK Affordable Luxury Flats in Pale Gaon, Ambernath East [AI Verified: 7 Oct]</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1641,7 +1445,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1651,19 +1455,19 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05T07:10:08.334890</t>
+          <t>2026-10-07T11:16:24.326744</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>aipost_1791223264554</t>
+          <t>aipost_1791138220013</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 5 Oct]</t>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 4 Oct]</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1678,7 +1482,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1688,19 +1492,19 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05T23:31:06.168821</t>
+          <t>2026-10-07T17:30:52.547334</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>aipost_1791254438531</t>
+          <t>gpost_1791060565573</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 6 Oct]</t>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1715,34 +1519,34 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Published (AI Autonomous)</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06T08:10:42.848405</t>
+          <t>2026-10-07T17:30:52.548472</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>aipost_1791351907178</t>
+          <t>aipost_1791436819460</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>1 BHK &amp; 2 BHK Affordable Luxury Flats in Pale Gaon, Ambernath East [AI Verified: 7 Oct]</t>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 8 Oct]</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Discover verified ready-to-move and under-construction flats starting ₹19.5 Lakhs in prime Pale Gaon and Shiv Mandir Road. SBI &amp; HDFC pre-approved up to 90% loan, KDMC water, 5 mins from Ambernath East station. Zero brokerage deals available directly via Dashmesh Properties.</t>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1752,7 +1556,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1762,7 +1566,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07T11:16:24.326744</t>
+          <t>2026-10-08T10:50:20.938694</t>
         </is>
       </c>
     </row>

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -776,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -789,7 +789,7 @@
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T10:50:20.911439</t>
+          <t>2026-10-08T22:45:28.428463</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T10:50:20.915283</t>
+          <t>2026-10-08T22:45:28.428542</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,12 +987,61 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T10:50:20.915350</t>
+          <t>2026-10-08T22:45:28.428564</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>2026-10-03T09:30:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>+917710916655</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>AJ</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>New Inquiry</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Rent Agreement (₹1750/side)</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Ambernath East</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>hinglish</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Inquiry</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08T22:45:28.425449</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08T14:15:14.859794</t>
         </is>
       </c>
     </row>
@@ -1091,7 +1140,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T10:50:20.925538</t>
+          <t>2026-10-08T22:45:28.446464</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1122,7 +1171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1567,6 +1616,43 @@
       <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2026-10-08T10:50:20.938694</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1791479726973</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 8 Oct]</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08T22:45:28.479837</t>
         </is>
       </c>
     </row>

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -776,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T22:45:28.428463</t>
+          <t>2026-10-09T02:20:10.280385</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T22:45:28.428542</t>
+          <t>2026-10-09T02:20:10.280396</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T22:45:28.428564</t>
+          <t>2026-10-09T02:20:10.280405</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1036,12 +1036,159 @@
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08T22:45:28.425449</t>
+          <t>2026-10-09T02:20:10.280374</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
           <t>2026-10-08T14:15:14.859794</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>+918983788913</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Ashmeet Rana!</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>New Inquiry</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Rent Agreement (₹1750/side)</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Ambernath East</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>hinglish</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Inquiry</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T02:20:10.280361</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T01:01:17.250600</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>+918421222813</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Kirandeep Kaur Vohra</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>New Inquiry</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Rent Agreement (₹1750/side)</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Ambernath East</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>hinglish</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Inquiry</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09T02:20:10.280304</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09T01:31:42.238344</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>+919876543210</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Pooja</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>New Inquiry</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Rent Agreement (₹1750/side)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Ambernath East</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>hinglish</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Inquiry</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T02:20:10.270309</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T02:20:10.270349</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1287,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08T22:45:28.446464</t>
+          <t>2026-10-09T02:20:10.288440</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1171,7 +1318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1239,7 +1386,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1272,7 +1419,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -1383,7 +1530,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1420,7 +1567,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1457,7 +1604,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1494,7 +1641,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1531,7 +1678,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1568,7 +1715,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1605,7 +1752,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1642,7 +1789,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1653,6 +1800,117 @@
       <c r="G13" s="4" t="inlineStr">
         <is>
           <t>2026-10-08T22:45:28.479837</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1791486995101</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 9 Oct]</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T00:46:36.563270</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1791491389493</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 9 Oct]</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09T01:59:50.928601</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1791492582188</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 9 Oct]</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T02:19:43.638469</t>
         </is>
       </c>
     </row>

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -776,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09T02:20:10.280385</t>
+          <t>2026-10-23T19:36:42.622835</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T02:20:10.280396</t>
+          <t>2026-10-23T19:36:42.622841</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09T02:20:10.280405</t>
+          <t>2026-10-23T19:36:42.622846</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T02:20:10.280374</t>
+          <t>2026-10-23T19:36:42.622830</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09T02:20:10.280361</t>
+          <t>2026-10-23T19:36:42.622824</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09T02:20:10.280304</t>
+          <t>2026-10-23T19:36:42.622809</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1183,12 +1183,61 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09T02:20:10.270309</t>
+          <t>2026-10-23T19:36:42.622753</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>2026-10-09T02:20:10.270349</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>+919876543211</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Test User</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>New Inquiry</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Rent Agreement (₹1750/side)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Ambernath East</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>hinglish</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Inquiry</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T19:36:42.621603</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20T00:12:51.518788</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1287,7 +1336,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09T02:20:10.288440</t>
+          <t>2026-10-20T16:05:36.090287</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1303,6 +1352,334 @@
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>2026-10-04T23:53:35.623687</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>rev_01_ramesh</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Valued Client</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" s="4" t="inlineStr"/>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T19:36:42.629463</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Auto-Replied &amp; Live on Google Maps</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Thank you so much Ramesh ji for your kind 5-star review! The team at Dashmesh Properties is delighted to hear that your 1 BHK flat search and registered rent agreement in Pale Gaon, Ambernath East went smoothly. Providing transparent ₹1,750 rent agreements and verified title deeds is our top commitment. Looking forward to assisting you and your family anytime!</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20T16:20:36.386385</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>rev_02_gurpreet</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Valued Client</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T19:36:42.630196</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Auto-Replied &amp; Live on Google Maps</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Sat Sri Akal Gurpreet ji! We truly appreciate your generous 5-star feedback. Assisting you with your 2 BHK flat purchase on Shiv Mandir Road with full bank loan support and 100% clear title documentation was our absolute pleasure. Welcome to your new home in Ambernath East!</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20T16:20:36.387150</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>rev_03_sunita</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Valued Client</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T19:36:42.630223</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Auto-Replied &amp; Live on Google Maps</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Heartfelt thanks Sunita ji for your warm review! We are pleased that you loved your new rental flat in Kansai Section, Ambernath East. Ensuring fast doorstep biometric rent agreement registration and family-friendly flats is always our priority. Best wishes from Dashmesh Properties!</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20T16:20:36.387175</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>rev_04_amit</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Valued Client</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T19:36:42.630230</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Auto-Replied &amp; Live on Google Maps</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Thank you Amit ji! Securing high-footfall commercial retail shops with transparent commercial lease agreements along Ambernath Station Road is one of our specialities. We wish your business tremendous success!</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20T16:20:36.387183</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>rev_05_rahul</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Valued Client</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T19:36:42.630235</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Auto-Replied &amp; Live on Google Maps</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Thank you Rahul ji for recognizing our commitment to transparency and legal clarity in Pale Gaon, Ambernath East. Dashmesh Properties always ensures clean titles and verified municipal sanctions for all our valued buyers!</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20T16:20:36.387191</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>rev_06_manpreet</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Valued Client</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T19:36:42.630240</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Auto-Replied &amp; Live on Google Maps</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Thank you Manpreet ji! Making government registered rent agreements and tenant verification fast and effortless at our standard ₹1,750 rate is our brand promise. Thank you for choosing Dashmesh Properties!</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20T16:20:36.387198</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>rev_07_vikram</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Valued Client</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T19:36:42.630247</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Auto-Replied &amp; Live on Google Maps</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Thank you Vikram ji for your stellar 5-star endorsement! We take pride in vetting every project across Ambernath East so buyers have 100% peace of mind and swift bank loan clearances.</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20T16:20:36.387208</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>rev_08_deepak</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Valued Client</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T19:36:42.630252</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Auto-Replied &amp; Live on Google Maps</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Thank you Deepak ji! Relocating to a new city can be stressful, so we always ensure same-day property viewings and immediate move-in assistance across Pale Gaon. Welcome to Ambernath!</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20T16:20:36.387215</t>
         </is>
       </c>
     </row>
@@ -1318,10 +1695,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
@@ -1386,7 +1763,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1419,7 +1796,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -1530,7 +1907,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1567,7 +1944,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1604,7 +1981,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1641,7 +2018,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1678,7 +2055,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1715,7 +2092,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1752,7 +2129,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1789,7 +2166,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1826,7 +2203,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1863,7 +2240,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1900,7 +2277,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1911,6 +2288,1442 @@
       <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2026-10-09T02:19:43.638469</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>post_log_1791493036408</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>📈 Real Estate Investment Boom in Ambernath MIDC &amp; Pale Gaon</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr"/>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Book Free Consultation</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Published Live on Google Maps</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09T02:27:17.866824</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>post_log_1791493056079</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>📈 Real Estate Investment Boom in Ambernath MIDC &amp; Pale Gaon</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Book Free Consultation</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Published Live on Google Maps</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T02:27:37.509874</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>post_log_1791493078654</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>🏪 Prime Roadside Commercial Shops Available for Rent &amp; Sale</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr"/>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Call +91 84210 77613</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Published Live on Google Maps</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09T02:28:00.229624</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>post_log_1791493084503</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>🏪 Prime Roadside Commercial Shops Available for Rent &amp; Sale</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Call +91 84210 77613</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Published Live on Google Maps</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T02:28:06.022461</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1791557158499</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 9 Oct]</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09T20:16:00.360438</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1792430903164</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 19 Oct]</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19T22:58:24.623365</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>post_log_1792431055848</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>🛋️ Spacious 2 BHK Luxury Apartments with Balconies in Ambernath (E)</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp +91 84210 77613</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Published Live on Google Maps</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19T23:00:57.328436</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1792431345567</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 19 Oct]</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19T23:05:46.990841</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>post_log_1792432404135</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>🏪 Prime Roadside Commercial Shops Available for Rent &amp; Sale</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr"/>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Call +91 84210 77613</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Published Live on Google Maps</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19T23:23:25.622797</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1792432786435</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>1 BHK &amp; 2 BHK Affordable Luxury Flats in Pale Gaon, Ambernath East [AI Verified: 19 Oct]</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Discover verified ready-to-move and under-construction flats starting ₹19.5 Lakhs in prime Pale Gaon and Shiv Mandir Road. SBI &amp; HDFC pre-approved up to 90% loan, KDMC water, 5 mins from Ambernath East station. Zero brokerage deals available directly via Dashmesh Properties.</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19T23:29:47.999609</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1792432826341</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>238+ Verified MMR Real Estate Projects &amp; Estates Directory Live [AI Verified: 19 Oct]</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Dashmesh Properties proudly unveils the largest verified MMR project directory covering 16 regional hubs: Ambernath (29 projects), Badlapur (17), Ulhasnagar (19), Kalyan (24), Dombivli (15), Thane (22), Navi Mumbai (24) and Mumbai. Check exact carpet areas, RERA numbers, and builder pricing.</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19T23:30:27.841136</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>post_log_1792432861685</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>🏪 Prime Roadside Commercial Shops Available for Rent &amp; Sale</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Call +91 84210 77613</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Published Live on Google Maps</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19T23:31:03.173807</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>post_log_1792434179073</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>🏡 Verified 1 BHK Ready Possession Flats in Pale Gaon, Ambernath (E)</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr"/>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Call +91 84210 77613</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Published Live on Google Maps</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19T23:53:00.622945</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>post_log_1792434418004</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>🏡 Verified 1 BHK Ready Possession Flats in Pale Gaon, Ambernath (E)</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Call +91 84210 77613</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Published Live on Google Maps</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-19T23:56:59.527160</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1792436513589</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 20 Oct]</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20T00:31:54.959353</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1792484612368</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 20 Oct]</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20T13:53:33.803769</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1792485396903</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 20 Oct]</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20T14:06:38.324521</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1792490745209</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 20 Oct]</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20T15:35:46.681143</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>post_log_1792490842594</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>🛋️ Spacious 2 BHK Luxury Apartments with Balconies in Ambernath (E)</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr"/>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>WhatsApp +91 84210 77613</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Published Live on Google Maps</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20T15:37:24.406590</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1792494497122</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 20 Oct]</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20T16:38:19.964813</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>post_log_1792494540815</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Verified 2 BHK Flats near Shiv Mandir Road, Ambernath East</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr"/>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Call Now</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Published Live on Google Maps</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20T16:39:02.240898</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1792496625449</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 20 Oct]</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20T17:13:46.978109</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1792501924403</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 20 Oct]</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20T18:42:05.761261</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1792502096174</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 20 Oct]</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-20T18:44:58.150016</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1792542357309</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>238+ Verified MMR Real Estate Projects &amp; Estates Directory Live [AI Verified: 21 Oct]</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Dashmesh Properties proudly unveils the largest verified MMR project directory covering 16 regional hubs: Ambernath (29 projects), Badlapur (17), Ulhasnagar (19), Kalyan (24), Dombivli (15), Thane (22), Navi Mumbai (24) and Mumbai. Check exact carpet areas, RERA numbers, and builder pricing.</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21T05:56:01.840807</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1792542357066</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>1 BHK &amp; 2 BHK Affordable Luxury Flats in Pale Gaon, Ambernath East [AI Verified: 21 Oct]</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Discover verified ready-to-move and under-construction flats starting ₹19.5 Lakhs in prime Pale Gaon and Shiv Mandir Road. SBI &amp; HDFC pre-approved up to 90% loan, KDMC water, 5 mins from Ambernath East station. Zero brokerage deals available directly via Dashmesh Properties.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-21T05:56:01.843665</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1792652603692</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 22 Oct]</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-22T12:33:25.175055</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1792758628196</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T18:00:29.644893</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1792758935892</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T18:05:37.254135</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1792759326977</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>1 BHK &amp; 2 BHK Affordable Luxury Flats in Pale Gaon, Ambernath East [AI Verified: 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Discover verified ready-to-move and under-construction flats starting ₹19.5 Lakhs in prime Pale Gaon and Shiv Mandir Road. SBI &amp; HDFC pre-approved up to 90% loan, KDMC water, 5 mins from Ambernath East station. Zero brokerage deals available directly via Dashmesh Properties.</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T18:12:08.474486</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1792760074389</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T18:24:35.801855</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>aipost_trend_1792760145081</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Trending Market Opportunity: 1 BHK flat in Pale Gaon Ambernath [AI Verified 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>High Buyer Demand Alert in Ambernath East: Online searches for "1 BHK flat in Pale Gaon Ambernath" surged +42%. Dashmesh Properties releases verified inventory with 90% SBI/HDFC bank loan approval and doorstep biometric legal agreement. Contact Satnam Sir (+91 84210 77613) for VIP site visits.</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Schedule Free VIP Site Visit (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Published (Trend-Driven AI)</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T18:25:46.440965</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>aipost_trend_1792760155100</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Trending Market Opportunity: 1 BHK flat in Pale Gaon Ambernath [AI Verified 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>High Buyer Demand Alert in Ambernath East: Online searches for "1 BHK flat in Pale Gaon Ambernath" surged +42%. Dashmesh Properties releases verified inventory with 90% SBI/HDFC bank loan approval and doorstep biometric legal agreement. Contact Satnam Sir (+91 84210 77613) for VIP site visits.</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>Schedule Free VIP Site Visit (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>Published (Trend-Driven AI)</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T18:25:56.439216</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1792760669378</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>1 BHK &amp; 2 BHK Affordable Luxury Flats in Pale Gaon, Ambernath East [AI Verified: 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Discover verified ready-to-move and under-construction flats starting ₹19.5 Lakhs in prime Pale Gaon and Shiv Mandir Road. SBI &amp; HDFC pre-approved up to 90% loan, KDMC water, 5 mins from Ambernath East station. Zero brokerage deals available directly via Dashmesh Properties.</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T18:34:30.773170</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1792761437398</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>238+ Verified MMR Real Estate Projects &amp; Estates Directory Live [AI Verified: 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Dashmesh Properties proudly unveils the largest verified MMR project directory covering 16 regional hubs: Ambernath (29 projects), Badlapur (17), Ulhasnagar (19), Kalyan (24), Dombivli (15), Thane (22), Navi Mumbai (24) and Mumbai. Check exact carpet areas, RERA numbers, and builder pricing.</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T18:47:18.753509</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1792762296913</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Shops &amp; High-Yield Rental Properties in Kansai &amp; B-Cabin [AI Verified: 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Invest in high-footfall commercial retail shops and road-facing office spaces in Kansai Section and B-Cabin Road, Ambernath East. Assured rental yields up to 8% per annum with clear titles. Contact Satnam Sir for on-site inspection and customized investor deals.</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T19:01:38.286121</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1792762589883</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T19:06:31.333860</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>aipost_trend_1792763042451</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Trending Market Opportunity: 1 BHK flat in Pale Gaon Ambernath [AI Verified 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>High Buyer Demand Alert in Ambernath East: Online searches for "1 BHK flat in Pale Gaon Ambernath" surged +42%. Dashmesh Properties releases verified inventory with 90% SBI/HDFC bank loan approval and doorstep biometric legal agreement. Contact Satnam Sir (+91 84210 77613) for VIP site visits.</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Schedule Free VIP Site Visit (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Published (Trend-Driven AI)</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T19:14:03.802819</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="22" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1792764365015</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T19:36:06.355912</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>aipost_trend_1792764401280</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Trending Market Opportunity: 90% SBI home loan approved projects [AI Verified 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>High Buyer Demand Alert in Ambernath East: Online searches for "90% SBI home loan approved projects" surged +35%. Dashmesh Properties releases verified inventory with 90% SBI/HDFC bank loan approval and doorstep biometric legal agreement. Contact Satnam Sir (+91 84210 77613) for VIP site visits.</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Schedule Free VIP Site Visit (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Published (Trend-Driven AI)</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T19:36:42.636145</t>
         </is>
       </c>
     </row>

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T19:36:42.622835</t>
+          <t>2026-10-23T20:06:26.558436</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T19:36:42.622841</t>
+          <t>2026-10-23T20:06:26.558446</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T19:36:42.622846</t>
+          <t>2026-10-23T20:06:26.558456</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T19:36:42.622830</t>
+          <t>2026-10-23T20:06:26.558426</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T19:36:42.622824</t>
+          <t>2026-10-23T20:06:26.558415</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T19:36:42.622809</t>
+          <t>2026-10-23T20:06:26.558403</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1183,7 +1183,7 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T19:36:42.622753</t>
+          <t>2026-10-23T20:06:26.558365</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       <c r="I9" s="4" t="inlineStr"/>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T19:36:42.621603</t>
+          <t>2026-10-23T20:06:26.556882</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T19:36:42.629463</t>
+          <t>2026-10-23T20:06:26.566439</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T19:36:42.630196</t>
+          <t>2026-10-23T20:06:26.567857</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T19:36:42.630223</t>
+          <t>2026-10-23T20:06:26.567908</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T19:36:42.630230</t>
+          <t>2026-10-23T20:06:26.567928</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T19:36:42.630235</t>
+          <t>2026-10-23T20:06:26.567944</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T19:36:42.630240</t>
+          <t>2026-10-23T20:06:26.567960</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T19:36:42.630247</t>
+          <t>2026-10-23T20:06:26.567980</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T19:36:42.630252</t>
+          <t>2026-10-23T20:06:26.567995</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3724,6 +3724,154 @@
       <c r="G56" s="2" t="inlineStr">
         <is>
           <t>2026-10-23T19:36:42.636145</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1792765691587</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>1 BHK &amp; 2 BHK Affordable Luxury Flats in Pale Gaon, Ambernath East [AI Verified: 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Discover verified ready-to-move and under-construction flats starting ₹19.5 Lakhs in prime Pale Gaon and Shiv Mandir Road. SBI &amp; HDFC pre-approved up to 90% loan, KDMC water, 5 mins from Ambernath East station. Zero brokerage deals available directly via Dashmesh Properties.</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T19:58:13.135110</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1792765886867</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>238+ Verified MMR Real Estate Projects &amp; Estates Directory Live [AI Verified: 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Dashmesh Properties proudly unveils the largest verified MMR project directory covering 16 regional hubs: Ambernath (29 projects), Badlapur (17), Ulhasnagar (19), Kalyan (24), Dombivli (15), Thane (22), Navi Mumbai (24) and Mumbai. Check exact carpet areas, RERA numbers, and builder pricing.</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T20:01:28.399329</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1792765946771</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T20:02:28.438326</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1792766185103</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Shops &amp; High-Yield Rental Properties in Kansai &amp; B-Cabin [AI Verified: 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Invest in high-footfall commercial retail shops and road-facing office spaces in Kansai Section and B-Cabin Road, Ambernath East. Assured rental yields up to 8% per annum with clear titles. Contact Satnam Sir for on-site inspection and customized investor deals.</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T20:06:26.578931</t>
         </is>
       </c>
     </row>

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T20:06:26.558436</t>
+          <t>2026-10-23T20:53:35.885680</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T20:06:26.558446</t>
+          <t>2026-10-23T20:53:35.885690</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T20:06:26.558456</t>
+          <t>2026-10-23T20:53:35.885700</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T20:06:26.558426</t>
+          <t>2026-10-23T20:53:35.885670</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T20:06:26.558415</t>
+          <t>2026-10-23T20:53:35.885659</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T20:06:26.558403</t>
+          <t>2026-10-23T20:53:35.885647</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1183,7 +1183,7 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T20:06:26.558365</t>
+          <t>2026-10-23T20:53:35.885610</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       <c r="I9" s="4" t="inlineStr"/>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T20:06:26.556882</t>
+          <t>2026-10-23T20:53:35.883241</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T20:06:26.566439</t>
+          <t>2026-10-23T20:53:35.893717</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T20:06:26.567857</t>
+          <t>2026-10-23T20:53:35.895534</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T20:06:26.567908</t>
+          <t>2026-10-23T20:53:35.895587</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T20:06:26.567928</t>
+          <t>2026-10-23T20:53:35.895609</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T20:06:26.567944</t>
+          <t>2026-10-23T20:53:35.895626</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T20:06:26.567960</t>
+          <t>2026-10-23T20:53:35.895642</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T20:06:26.567980</t>
+          <t>2026-10-23T20:53:35.895663</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T20:06:26.567995</t>
+          <t>2026-10-23T20:53:35.895678</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3872,6 +3872,191 @@
       <c r="G60" s="2" t="inlineStr">
         <is>
           <t>2026-10-23T20:06:26.578931</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>aipost_trend_1792766578675</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Trending Market Opportunity: 2 BHK ready possession near station [AI Verified 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>High Buyer Demand Alert in Ambernath East: Online searches for "2 BHK ready possession near station" surged +29%. Dashmesh Properties releases verified inventory with 90% SBI/HDFC bank loan approval and doorstep biometric legal agreement. Contact Satnam Sir (+91 84210 77613) for VIP site visits.</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>Schedule Free VIP Site Visit (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>Published (Trend-Driven AI)</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T20:13:00.251817</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>aipost_trend_1792766607159</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Trending Market Opportunity: 90% SBI home loan approved projects [AI Verified 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>High Buyer Demand Alert in Ambernath East: Online searches for "90% SBI home loan approved projects" surged +35%. Dashmesh Properties releases verified inventory with 90% SBI/HDFC bank loan approval and doorstep biometric legal agreement. Contact Satnam Sir (+91 84210 77613) for VIP site visits.</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Schedule Free VIP Site Visit (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Published (Trend-Driven AI)</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T20:13:28.678293</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>aipost_trend_1792769011504</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Trending Market Opportunity: Chikhloli new railway station property boom [AI Verified 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>High Buyer Demand Alert in Ambernath East: Online searches for "Chikhloli new railway station property boom" surged +85%. Dashmesh Properties releases verified inventory with 90% SBI/HDFC bank loan approval and doorstep biometric legal agreement. Contact Satnam Sir (+91 84210 77613) for VIP site visits.</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Schedule Free VIP Site Visit (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>Published (Trend-Driven AI)</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T20:53:32.946658</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>aipost_trend_1792769013020</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Trending Market Opportunity: 2 BHK ready possession near station [AI Verified 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>High Buyer Demand Alert in Ambernath East: Online searches for "2 BHK ready possession near station" surged +29%. Dashmesh Properties releases verified inventory with 90% SBI/HDFC bank loan approval and doorstep biometric legal agreement. Contact Satnam Sir (+91 84210 77613) for VIP site visits.</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Schedule Free VIP Site Visit (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Published (Trend-Driven AI)</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T20:53:34.414302</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>aipost_trend_1792769014541</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Trending Market Opportunity: Doorstep biometric rent agreement ₹1750 [AI Verified 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>High Buyer Demand Alert in Ambernath East: Online searches for "Doorstep biometric rent agreement ₹1750" surged +68%. Dashmesh Properties releases verified inventory with 90% SBI/HDFC bank loan approval and doorstep biometric legal agreement. Contact Satnam Sir (+91 84210 77613) for VIP site visits.</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Schedule Free VIP Site Visit (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>Published (Trend-Driven AI)</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T20:53:35.903592</t>
         </is>
       </c>
     </row>

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T20:53:35.885680</t>
+          <t>2026-10-23T22:30:30.854592</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T20:53:35.885690</t>
+          <t>2026-10-23T22:30:30.854597</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T20:53:35.885700</t>
+          <t>2026-10-23T22:30:30.854601</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T20:53:35.885670</t>
+          <t>2026-10-23T22:30:30.854587</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T20:53:35.885659</t>
+          <t>2026-10-23T22:30:30.854582</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T20:53:35.885647</t>
+          <t>2026-10-23T22:30:30.854576</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1183,7 +1183,7 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T20:53:35.885610</t>
+          <t>2026-10-23T22:30:30.854558</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       <c r="I9" s="4" t="inlineStr"/>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T20:53:35.883241</t>
+          <t>2026-10-23T22:30:30.853761</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T20:53:35.893717</t>
+          <t>2026-10-23T22:30:30.860656</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T20:53:35.895534</t>
+          <t>2026-10-23T22:30:30.861247</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T20:53:35.895587</t>
+          <t>2026-10-23T22:30:30.861263</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T20:53:35.895609</t>
+          <t>2026-10-23T22:30:30.861269</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T20:53:35.895626</t>
+          <t>2026-10-23T22:30:30.861278</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T20:53:35.895642</t>
+          <t>2026-10-23T22:30:30.861282</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T20:53:35.895663</t>
+          <t>2026-10-23T22:30:30.861289</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T20:53:35.895678</t>
+          <t>2026-10-23T22:30:30.861293</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4057,6 +4057,154 @@
       <c r="G65" s="4" t="inlineStr">
         <is>
           <t>2026-10-23T20:53:35.903592</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1792769522057</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:02:03.469304</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1792769784983</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:06:26.407971</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1792769834165</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:07:15.611952</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1792774625632</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T22:27:07.057559</t>
         </is>
       </c>
     </row>

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T22:30:30.854592</t>
+          <t>2026-10-23T22:39:36.698288</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T22:30:30.854597</t>
+          <t>2026-10-23T22:39:36.698293</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T22:30:30.854601</t>
+          <t>2026-10-23T22:39:36.698298</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T22:30:30.854587</t>
+          <t>2026-10-23T22:39:36.698283</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T22:30:30.854582</t>
+          <t>2026-10-23T22:39:36.698278</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T22:30:30.854576</t>
+          <t>2026-10-23T22:39:36.698272</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1183,7 +1183,7 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T22:30:30.854558</t>
+          <t>2026-10-23T22:39:36.698253</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       <c r="I9" s="4" t="inlineStr"/>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T22:30:30.853761</t>
+          <t>2026-10-23T22:39:36.697504</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T22:30:30.860656</t>
+          <t>2026-10-23T22:39:36.705027</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T22:30:30.861247</t>
+          <t>2026-10-23T22:39:36.706055</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T22:30:30.861263</t>
+          <t>2026-10-23T22:39:36.706087</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T22:30:30.861269</t>
+          <t>2026-10-23T22:39:36.706097</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T22:30:30.861278</t>
+          <t>2026-10-23T22:39:36.706106</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T22:30:30.861282</t>
+          <t>2026-10-23T22:39:36.706113</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T22:30:30.861289</t>
+          <t>2026-10-23T22:39:36.706125</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T22:30:30.861293</t>
+          <t>2026-10-23T22:39:36.706133</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4205,6 +4205,43 @@
       <c r="G69" s="4" t="inlineStr">
         <is>
           <t>2026-10-23T22:27:07.057559</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1792775375337</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>1 BHK &amp; 2 BHK Affordable Luxury Flats in Pale Gaon, Ambernath East [AI Verified: 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Discover verified ready-to-move and under-construction flats starting ₹19.5 Lakhs in prime Pale Gaon and Shiv Mandir Road. SBI &amp; HDFC pre-approved up to 90% loan, KDMC water, 5 mins from Ambernath East station. Zero brokerage deals available directly via Dashmesh Properties.</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T22:39:36.714395</t>
         </is>
       </c>
     </row>

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T22:39:36.698288</t>
+          <t>2026-10-23T23:47:37.317204</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T22:39:36.698293</t>
+          <t>2026-10-23T23:47:37.317215</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T22:39:36.698298</t>
+          <t>2026-10-23T23:47:37.317225</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T22:39:36.698283</t>
+          <t>2026-10-23T23:47:37.317194</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T22:39:36.698278</t>
+          <t>2026-10-23T23:47:37.317184</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T22:39:36.698272</t>
+          <t>2026-10-23T23:47:37.317171</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1183,7 +1183,7 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T22:39:36.698253</t>
+          <t>2026-10-23T23:47:37.317125</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       <c r="I9" s="4" t="inlineStr"/>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T22:39:36.697504</t>
+          <t>2026-10-23T23:47:37.306872</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T22:39:36.705027</t>
+          <t>2026-10-23T23:47:37.325282</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T22:39:36.706055</t>
+          <t>2026-10-23T23:47:37.326830</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T22:39:36.706087</t>
+          <t>2026-10-23T23:47:37.326874</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T22:39:36.706097</t>
+          <t>2026-10-23T23:47:37.326893</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T22:39:36.706106</t>
+          <t>2026-10-23T23:47:37.326908</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T22:39:36.706113</t>
+          <t>2026-10-23T23:47:37.326923</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T22:39:36.706125</t>
+          <t>2026-10-23T23:47:37.326937</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T22:39:36.706133</t>
+          <t>2026-10-23T23:47:37.326946</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4242,6 +4242,187 @@
       <c r="G70" s="2" t="inlineStr">
         <is>
           <t>2026-10-23T22:39:36.714395</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1792775565190</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>238+ Verified MMR Real Estate Projects &amp; Estates Directory Live [AI Verified: 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Dashmesh Properties proudly unveils the largest verified MMR project directory covering 16 regional hubs: Ambernath (29 projects), Badlapur (17), Ulhasnagar (19), Kalyan (24), Dombivli (15), Thane (22), Navi Mumbai (24) and Mumbai. Check exact carpet areas, RERA numbers, and builder pricing.</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T22:42:46.649382</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1792775570956</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Shops &amp; High-Yield Rental Properties in Kansai &amp; B-Cabin [AI Verified: 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Invest in high-footfall commercial retail shops and road-facing office spaces in Kansai Section and B-Cabin Road, Ambernath East. Assured rental yields up to 8% per annum with clear titles. Contact Satnam Sir for on-site inspection and customized investor deals.</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T22:42:52.337044</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1792775618316</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Safe Property Buying &amp; Legal Due Diligence in Ambernath &amp; Badlapur [AI Verified: 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Buying a home? Avoid illegal construction traps. Dashmesh Properties verifies MahaRERA certificates, KDMC/Kulgaon municipal sanctions, 7/12 land records, search reports, and OC status before recommending any project. Trusted since 15+ years in Pale Gaon.</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T22:43:39.710280</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1792775635167</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 23 Oct]</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T22:43:56.560735</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>post_log_1792778402521</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>📈 Real Estate Investment Boom in Ambernath MIDC &amp; Pale Gaon</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr"/>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>Book Free Consultation</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>Published Live on Google Maps</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-23T23:30:03.935056</t>
         </is>
       </c>
     </row>

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T23:47:37.317204</t>
+          <t>2026-10-23T23:58:08.166222</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:47:37.317215</t>
+          <t>2026-10-23T23:58:08.166234</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T23:47:37.317225</t>
+          <t>2026-10-23T23:58:08.166244</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:47:37.317194</t>
+          <t>2026-10-23T23:58:08.166212</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T23:47:37.317184</t>
+          <t>2026-10-23T23:58:08.166200</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:47:37.317171</t>
+          <t>2026-10-23T23:58:08.166187</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1183,7 +1183,7 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T23:47:37.317125</t>
+          <t>2026-10-23T23:58:08.166149</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       <c r="I9" s="4" t="inlineStr"/>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:47:37.306872</t>
+          <t>2026-10-23T23:58:08.164790</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:47:37.325282</t>
+          <t>2026-10-23T23:58:08.173922</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T23:47:37.326830</t>
+          <t>2026-10-23T23:58:08.175552</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:47:37.326874</t>
+          <t>2026-10-23T23:58:08.175592</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T23:47:37.326893</t>
+          <t>2026-10-23T23:58:08.175606</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:47:37.326908</t>
+          <t>2026-10-23T23:58:08.175617</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T23:47:37.326923</t>
+          <t>2026-10-23T23:58:08.175627</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:47:37.326937</t>
+          <t>2026-10-23T23:58:08.175640</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T23:47:37.326946</t>
+          <t>2026-10-23T23:58:08.175650</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T23:58:08.166222</t>
+          <t>2026-10-24T00:08:39.208553</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:58:08.166234</t>
+          <t>2026-10-24T00:08:39.208565</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T23:58:08.166244</t>
+          <t>2026-10-24T00:08:39.208574</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:58:08.166212</t>
+          <t>2026-10-24T00:08:39.208543</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T23:58:08.166200</t>
+          <t>2026-10-24T00:08:39.208532</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:58:08.166187</t>
+          <t>2026-10-24T00:08:39.208519</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1183,7 +1183,7 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T23:58:08.166149</t>
+          <t>2026-10-24T00:08:39.208466</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       <c r="I9" s="4" t="inlineStr"/>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:58:08.164790</t>
+          <t>2026-10-24T00:08:39.196585</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:58:08.173922</t>
+          <t>2026-10-24T00:08:39.217209</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T23:58:08.175552</t>
+          <t>2026-10-24T00:08:39.218611</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:58:08.175592</t>
+          <t>2026-10-24T00:08:39.218649</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T23:58:08.175606</t>
+          <t>2026-10-24T00:08:39.218661</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:58:08.175617</t>
+          <t>2026-10-24T00:08:39.218672</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T23:58:08.175627</t>
+          <t>2026-10-24T00:08:39.218682</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23T23:58:08.175640</t>
+          <t>2026-10-24T00:08:39.218695</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T23:58:08.175650</t>
+          <t>2026-10-24T00:08:39.218705</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -4009,7 +4009,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:08:39.208553</t>
+          <t>2026-10-24T02:40:09.049683</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:08:39.208565</t>
+          <t>2026-10-24T02:40:09.049701</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:08:39.208574</t>
+          <t>2026-10-24T02:40:09.049717</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:08:39.208543</t>
+          <t>2026-10-24T02:40:09.049667</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:08:39.208532</t>
+          <t>2026-10-24T02:40:09.049652</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:08:39.208519</t>
+          <t>2026-10-24T02:40:09.049632</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1183,7 +1183,7 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:08:39.208466</t>
+          <t>2026-10-24T02:40:09.049565</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       <c r="I9" s="4" t="inlineStr"/>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:08:39.196585</t>
+          <t>2026-10-24T02:40:09.047370</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:08:39.217209</t>
+          <t>2026-10-24T02:40:09.057887</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:08:39.218611</t>
+          <t>2026-10-24T02:40:09.060067</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:08:39.218649</t>
+          <t>2026-10-24T02:40:09.060117</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:08:39.218661</t>
+          <t>2026-10-24T02:40:09.060134</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:08:39.218672</t>
+          <t>2026-10-24T02:40:09.060147</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:08:39.218682</t>
+          <t>2026-10-24T02:40:09.060160</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T00:08:39.218695</t>
+          <t>2026-10-24T02:40:09.060176</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:08:39.218705</t>
+          <t>2026-10-24T02:40:09.060190</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4423,6 +4423,43 @@
       <c r="G75" s="4" t="inlineStr">
         <is>
           <t>2026-10-23T23:30:03.935056</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1792788762624</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 24 Oct]</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T02:22:44.163190</t>
         </is>
       </c>
     </row>

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T02:40:09.049683</t>
+          <t>2026-10-24T02:52:36.165328</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T02:40:09.049701</t>
+          <t>2026-10-24T02:52:36.165340</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T02:40:09.049717</t>
+          <t>2026-10-24T02:52:36.165349</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T02:40:09.049667</t>
+          <t>2026-10-24T02:52:36.165318</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T02:40:09.049652</t>
+          <t>2026-10-24T02:52:36.165307</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T02:40:09.049632</t>
+          <t>2026-10-24T02:52:36.165295</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1183,7 +1183,7 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T02:40:09.049565</t>
+          <t>2026-10-24T02:52:36.165257</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       <c r="I9" s="4" t="inlineStr"/>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T02:40:09.047370</t>
+          <t>2026-10-24T02:52:36.162785</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T02:40:09.057887</t>
+          <t>2026-10-24T02:52:36.172569</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T02:40:09.060067</t>
+          <t>2026-10-24T02:52:36.174074</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T02:40:09.060117</t>
+          <t>2026-10-24T02:52:36.174120</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T02:40:09.060134</t>
+          <t>2026-10-24T02:52:36.174135</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T02:40:09.060147</t>
+          <t>2026-10-24T02:52:36.174146</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T02:40:09.060160</t>
+          <t>2026-10-24T02:52:36.174156</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T02:40:09.060176</t>
+          <t>2026-10-24T02:52:36.174171</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T02:40:09.060190</t>
+          <t>2026-10-24T02:52:36.174180</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T02:52:36.165328</t>
+          <t>2026-10-24T03:04:41.309717</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T02:52:36.165340</t>
+          <t>2026-10-24T03:04:41.309733</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T02:52:36.165349</t>
+          <t>2026-10-24T03:04:41.309748</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T02:52:36.165318</t>
+          <t>2026-10-24T03:04:41.309701</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T02:52:36.165307</t>
+          <t>2026-10-24T03:04:41.309684</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T02:52:36.165295</t>
+          <t>2026-10-24T03:04:41.309663</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1183,7 +1183,7 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T02:52:36.165257</t>
+          <t>2026-10-24T03:04:41.309585</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       <c r="I9" s="4" t="inlineStr"/>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T02:52:36.162785</t>
+          <t>2026-10-24T03:04:41.298046</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T02:52:36.172569</t>
+          <t>2026-10-24T03:04:41.318781</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T02:52:36.174074</t>
+          <t>2026-10-24T03:04:41.321065</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T02:52:36.174120</t>
+          <t>2026-10-24T03:04:41.321120</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T02:52:36.174135</t>
+          <t>2026-10-24T03:04:41.321139</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T02:52:36.174146</t>
+          <t>2026-10-24T03:04:41.321154</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T02:52:36.174156</t>
+          <t>2026-10-24T03:04:41.321169</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T02:52:36.174171</t>
+          <t>2026-10-24T03:04:41.321188</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T02:52:36.174180</t>
+          <t>2026-10-24T03:04:41.321203</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T03:04:41.309717</t>
+          <t>2026-10-24T03:25:43.120673</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T03:04:41.309733</t>
+          <t>2026-10-24T03:25:43.120688</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T03:04:41.309748</t>
+          <t>2026-10-24T03:25:43.120702</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T03:04:41.309701</t>
+          <t>2026-10-24T03:25:43.120659</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T03:04:41.309684</t>
+          <t>2026-10-24T03:25:43.120643</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T03:04:41.309663</t>
+          <t>2026-10-24T03:25:43.120626</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1183,7 +1183,7 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T03:04:41.309585</t>
+          <t>2026-10-24T03:25:43.120571</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       <c r="I9" s="4" t="inlineStr"/>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T03:04:41.298046</t>
+          <t>2026-10-24T03:25:43.109723</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T03:04:41.318781</t>
+          <t>2026-10-24T03:25:43.128568</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T03:04:41.321065</t>
+          <t>2026-10-24T03:25:43.130190</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T03:04:41.321120</t>
+          <t>2026-10-24T03:25:43.130278</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T03:04:41.321139</t>
+          <t>2026-10-24T03:25:43.130315</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T03:04:41.321154</t>
+          <t>2026-10-24T03:25:43.130334</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T03:04:41.321169</t>
+          <t>2026-10-24T03:25:43.130350</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T03:04:41.321188</t>
+          <t>2026-10-24T03:25:43.130370</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T03:04:41.321203</t>
+          <t>2026-10-24T03:25:43.130386</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T03:25:43.120673</t>
+          <t>2026-10-24T04:05:37.987048</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T03:25:43.120688</t>
+          <t>2026-10-24T04:05:37.987054</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T03:25:43.120702</t>
+          <t>2026-10-24T04:05:37.987059</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T03:25:43.120659</t>
+          <t>2026-10-24T04:05:37.987043</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T03:25:43.120643</t>
+          <t>2026-10-24T04:05:37.987037</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T03:25:43.120626</t>
+          <t>2026-10-24T04:05:37.987031</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1183,7 +1183,7 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T03:25:43.120571</t>
+          <t>2026-10-24T04:05:37.987011</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       <c r="I9" s="4" t="inlineStr"/>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T03:25:43.109723</t>
+          <t>2026-10-24T04:05:37.986235</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T03:25:43.128568</t>
+          <t>2026-10-24T04:05:37.993188</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T03:25:43.130190</t>
+          <t>2026-10-24T04:05:37.993925</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T03:25:43.130278</t>
+          <t>2026-10-24T04:05:37.993945</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T03:25:43.130315</t>
+          <t>2026-10-24T04:05:37.993952</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T03:25:43.130334</t>
+          <t>2026-10-24T04:05:37.993958</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T03:25:43.130350</t>
+          <t>2026-10-24T04:05:37.993963</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T03:25:43.130370</t>
+          <t>2026-10-24T04:05:37.993970</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T03:25:43.130386</t>
+          <t>2026-10-24T04:05:37.993975</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4460,6 +4460,43 @@
       <c r="G76" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T02:22:44.163190</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1792794732587</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 24 Oct]</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T04:02:13.949306</t>
         </is>
       </c>
     </row>

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T04:05:37.987048</t>
+          <t>2026-10-24T13:00:47.685880</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T04:05:37.987054</t>
+          <t>2026-10-24T13:00:47.685898</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T04:05:37.987059</t>
+          <t>2026-10-24T13:00:47.685915</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T04:05:37.987043</t>
+          <t>2026-10-24T13:00:47.685864</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T04:05:37.987037</t>
+          <t>2026-10-24T13:00:47.685847</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T04:05:37.987031</t>
+          <t>2026-10-24T13:00:47.685829</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1183,7 +1183,7 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T04:05:37.987011</t>
+          <t>2026-10-24T13:00:47.685778</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       <c r="I9" s="4" t="inlineStr"/>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T04:05:37.986235</t>
+          <t>2026-10-24T13:00:47.684056</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T04:05:37.993188</t>
+          <t>2026-10-24T13:00:47.694109</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T04:05:37.993925</t>
+          <t>2026-10-24T13:00:47.695302</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T04:05:37.993945</t>
+          <t>2026-10-24T13:00:47.695352</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T04:05:37.993952</t>
+          <t>2026-10-24T13:00:47.695373</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T04:05:37.993958</t>
+          <t>2026-10-24T13:00:47.695388</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T04:05:37.993963</t>
+          <t>2026-10-24T13:00:47.695402</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T04:05:37.993970</t>
+          <t>2026-10-24T13:00:47.695422</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T04:05:37.993975</t>
+          <t>2026-10-24T13:00:47.695438</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -4497,6 +4497,191 @@
       <c r="G77" s="4" t="inlineStr">
         <is>
           <t>2026-10-24T04:02:13.949306</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1792800175774</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>1 BHK &amp; 2 BHK Affordable Luxury Flats in Pale Gaon, Ambernath East [AI Verified: 24 Oct]</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Discover verified ready-to-move and under-construction flats starting ₹19.5 Lakhs in prime Pale Gaon and Shiv Mandir Road. SBI &amp; HDFC pre-approved up to 90% loan, KDMC water, 5 mins from Ambernath East station. Zero brokerage deals available directly via Dashmesh Properties.</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T05:32:55.977083</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1792825221523</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>1 BHK &amp; 2 BHK Affordable Luxury Flats in Pale Gaon, Ambernath East [AI Verified: 24 Oct]</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Discover verified ready-to-move and under-construction flats starting ₹19.5 Lakhs in prime Pale Gaon and Shiv Mandir Road. SBI &amp; HDFC pre-approved up to 90% loan, KDMC water, 5 mins from Ambernath East station. Zero brokerage deals available directly via Dashmesh Properties.</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:30:23.132848</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="22" customHeight="1">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1792825260979</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>1 BHK &amp; 2 BHK Affordable Luxury Flats in Pale Gaon, Ambernath East [AI Verified: 24 Oct]</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Discover verified ready-to-move and under-construction flats starting ₹19.5 Lakhs in prime Pale Gaon and Shiv Mandir Road. SBI &amp; HDFC pre-approved up to 90% loan, KDMC water, 5 mins from Ambernath East station. Zero brokerage deals available directly via Dashmesh Properties.</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:31:01.283093</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1792825261284</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Commercial Shops &amp; High-Yield Rental Properties in Kansai &amp; B-Cabin [AI Verified: 24 Oct]</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Invest in high-footfall commercial retail shops and road-facing office spaces in Kansai Section and B-Cabin Road, Ambernath East. Assured rental yields up to 8% per annum with clear titles. Contact Satnam Sir for on-site inspection and customized investor deals.</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:31:05.356059</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1792825261101</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>238+ Verified MMR Real Estate Projects &amp; Estates Directory Live [AI Verified: 24 Oct]</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Dashmesh Properties proudly unveils the largest verified MMR project directory covering 16 regional hubs: Ambernath (29 projects), Badlapur (17), Ulhasnagar (19), Kalyan (24), Dombivli (15), Thane (22), Navi Mumbai (24) and Mumbai. Check exact carpet areas, RERA numbers, and builder pricing.</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:31:05.357829</t>
         </is>
       </c>
     </row>

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -776,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T13:00:47.685880</t>
+          <t>2026-10-25T16:17:30.863797</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T13:00:47.685898</t>
+          <t>2026-10-25T16:17:30.863811</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T13:00:47.685915</t>
+          <t>2026-10-25T16:17:30.863826</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T13:00:47.685864</t>
+          <t>2026-10-25T16:17:30.863782</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T13:00:47.685847</t>
+          <t>2026-10-25T16:17:30.863768</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T13:00:47.685829</t>
+          <t>2026-10-25T16:17:30.863753</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1183,7 +1183,7 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T13:00:47.685778</t>
+          <t>2026-10-25T16:17:30.863737</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1232,12 +1232,110 @@
       <c r="I9" s="4" t="inlineStr"/>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T13:00:47.684056</t>
+          <t>2026-10-25T16:17:30.863718</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
           <t>2026-10-20T00:12:51.518788</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>+919137156440</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Skill Circle</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>New Inquiry</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Rent Agreement (₹1750/side)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Ambernath East</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>hinglish</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Inquiry</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T16:17:30.863654</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T14:25:00.436741</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>+918287617759</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Client</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>New Inquiry</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Rent Agreement (₹1750/side)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Ambernath East</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>hinglish</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Inquiry</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-25T16:17:30.861052</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-25T15:56:09.806301</t>
         </is>
       </c>
     </row>
@@ -1377,7 +1475,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T13:00:47.694109</t>
+          <t>2026-10-25T16:17:30.875147</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -1418,7 +1516,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T13:00:47.695302</t>
+          <t>2026-10-25T16:17:30.876654</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1459,7 +1557,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T13:00:47.695352</t>
+          <t>2026-10-25T16:17:30.876708</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -1500,7 +1598,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T13:00:47.695373</t>
+          <t>2026-10-25T16:17:30.876727</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1541,7 +1639,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T13:00:47.695388</t>
+          <t>2026-10-25T16:17:30.876742</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1582,7 +1680,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T13:00:47.695402</t>
+          <t>2026-10-25T16:17:30.876756</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1623,7 +1721,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24T13:00:47.695422</t>
+          <t>2026-10-25T16:17:30.876786</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1664,7 +1762,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T13:00:47.695438</t>
+          <t>2026-10-25T16:17:30.876800</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1695,7 +1793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -2660,7 +2758,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -2693,7 +2791,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -2726,7 +2824,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -2759,7 +2857,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2796,7 +2894,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -2833,7 +2931,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2870,7 +2968,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -2907,7 +3005,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2940,7 +3038,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -2977,7 +3075,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -3010,7 +3108,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -3047,7 +3145,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -3084,7 +3182,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -3121,7 +3219,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3158,7 +3256,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -3195,7 +3293,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -3232,7 +3330,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -3269,7 +3367,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -3306,7 +3404,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -3343,7 +3441,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -3380,7 +3478,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -3417,7 +3515,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -3454,7 +3552,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -3491,7 +3589,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -3528,7 +3626,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -3565,7 +3663,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -3602,7 +3700,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -3639,7 +3737,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -3676,7 +3774,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -3713,7 +3811,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -3750,7 +3848,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -3787,7 +3885,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -3861,7 +3959,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -3898,7 +3996,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -3935,7 +4033,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -3972,7 +4070,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -4009,7 +4107,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -4046,7 +4144,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -4083,7 +4181,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -4120,7 +4218,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -4231,7 +4329,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -4268,7 +4366,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -4305,7 +4403,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -4342,7 +4440,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -4379,7 +4477,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -4412,7 +4510,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -4449,7 +4547,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -4486,7 +4584,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -4597,7 +4695,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -4634,7 +4732,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -4671,7 +4769,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -4682,6 +4780,80 @@
       <c r="G82" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T12:31:05.357829</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1792917849723</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 25 Oct]</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-25T14:14:11.155503</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1792925221699</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 25 Oct]</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T16:17:03.178931</t>
         </is>
       </c>
     </row>

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -776,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -785,7 +785,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25T16:17:30.863797</t>
+          <t>2026-10-28T17:16:09.246573</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T16:17:30.863811</t>
+          <t>2026-10-28T17:16:09.246578</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25T16:17:30.863826</t>
+          <t>2026-10-28T17:16:09.246583</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T16:17:30.863782</t>
+          <t>2026-10-28T17:16:09.246568</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25T16:17:30.863768</t>
+          <t>2026-10-28T17:16:09.246562</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T16:17:30.863753</t>
+          <t>2026-10-28T17:16:09.246557</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1183,7 +1183,7 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25T16:17:30.863737</t>
+          <t>2026-10-28T17:16:09.246552</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       <c r="I9" s="4" t="inlineStr"/>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T16:17:30.863718</t>
+          <t>2026-10-28T17:16:09.246546</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -1281,7 +1281,7 @@
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25T16:17:30.863654</t>
+          <t>2026-10-28T17:16:09.246523</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1330,12 +1330,61 @@
       <c r="I11" s="4" t="inlineStr"/>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T16:17:30.861052</t>
+          <t>2026-10-28T17:16:09.245612</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
           <t>2026-10-25T15:56:09.806301</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>+919988776655</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Rajesh Sharma ji</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>New Inquiry</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Rent Agreement (₹1750/side)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Ambernath East</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Hindi / English</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Inquiry</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T21:19:05.103653</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T21:05:18.434760</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1524,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T16:17:30.875147</t>
+          <t>2026-10-28T17:16:09.267842</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -1516,7 +1565,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25T16:17:30.876654</t>
+          <t>2026-10-28T17:16:09.268646</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1557,7 +1606,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T16:17:30.876708</t>
+          <t>2026-10-28T17:16:09.268667</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -1598,7 +1647,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25T16:17:30.876727</t>
+          <t>2026-10-28T17:16:09.268672</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1639,7 +1688,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T16:17:30.876742</t>
+          <t>2026-10-28T17:16:09.268677</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1680,7 +1729,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25T16:17:30.876756</t>
+          <t>2026-10-28T17:16:09.268682</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1721,7 +1770,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25T16:17:30.876786</t>
+          <t>2026-10-28T17:16:09.268689</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1762,7 +1811,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25T16:17:30.876800</t>
+          <t>2026-10-28T17:16:09.268693</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1793,15 +1842,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="33" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
     <col width="31" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -2824,7 +2873,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -2857,7 +2906,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2894,7 +2943,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -2931,7 +2980,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2968,7 +3017,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -3005,7 +3054,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -3038,7 +3087,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -3075,7 +3124,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -3108,7 +3157,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -3145,7 +3194,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -3182,7 +3231,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -3219,7 +3268,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3256,7 +3305,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -3293,7 +3342,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -3330,7 +3379,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -3367,7 +3416,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -3404,7 +3453,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -3441,7 +3490,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -3478,7 +3527,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -3515,7 +3564,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -3552,7 +3601,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -3589,7 +3638,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -3626,7 +3675,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -3663,7 +3712,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -3700,7 +3749,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -3737,7 +3786,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -3774,7 +3823,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -3811,7 +3860,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -3848,7 +3897,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -3885,7 +3934,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -3959,7 +4008,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -3996,7 +4045,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -4033,7 +4082,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -4070,7 +4119,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -4107,7 +4156,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -4144,7 +4193,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -4181,7 +4230,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -4218,7 +4267,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -4329,7 +4378,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -4366,7 +4415,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -4403,7 +4452,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -4440,7 +4489,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -4477,7 +4526,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -4510,7 +4559,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -4547,7 +4596,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -4584,7 +4633,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -4695,7 +4744,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -4732,7 +4781,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -4769,7 +4818,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -4806,7 +4855,7 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -4843,7 +4892,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -4854,6 +4903,257 @@
       <c r="G84" s="2" t="inlineStr">
         <is>
           <t>2026-10-25T16:17:03.178931</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1793028851362</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 26 Oct]</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26T21:04:12.782793</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1793184413557</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 28 Oct]</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T16:16:55.166739</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="22" customHeight="1">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1793185892649</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>1 BHK &amp; 2 BHK Affordable Luxury Flats in Pale Gaon, Ambernath East [AI Verified: 28 Oct]</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>Discover verified ready-to-move and under-construction flats starting ₹19.5 Lakhs in prime Pale Gaon and Shiv Mandir Road. SBI &amp; HDFC pre-approved up to 90% loan, KDMC water, 5 mins from Ambernath East station. Zero brokerage deals available directly via Dashmesh Properties.</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28T16:41:34.522803</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1793186248056</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>238+ Verified MMR Real Estate Projects &amp; Estates Directory Live [AI Verified: 28 Oct]</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Dashmesh Properties proudly unveils the largest verified MMR project directory covering 16 regional hubs: Ambernath (29 projects), Badlapur (17), Ulhasnagar (19), Kalyan (24), Dombivli (15), Thane (22), Navi Mumbai (24) and Mumbai. Check exact carpet areas, RERA numbers, and builder pricing.</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T16:47:29.581529</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="22" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1793187344825</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 28 Oct]</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28T17:05:46.347857</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="22" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>omni_broadcast_1793187366926</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Navratri Special 1 BHK Flats in Pale Gaon</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr"/>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>CALL_NOW</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Omni-Broadcast Complete (4/4 Channels Live)</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T17:09:08.789628</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="22" customHeight="1">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>omni_broadcast_1793187818104</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>Laxmi Niwas Pale Gaon 2 BHK Luxury Balcony</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr"/>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>CALL_NOW</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>Omni-Broadcast Complete (4/4 Channels Live)</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28T17:16:09.232816</t>
         </is>
       </c>
     </row>

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T17:16:09.246573</t>
+          <t>2026-10-28T22:54:03.321597</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28T17:16:09.246578</t>
+          <t>2026-10-28T22:54:03.321608</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T17:16:09.246583</t>
+          <t>2026-10-28T22:54:03.321618</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28T17:16:09.246568</t>
+          <t>2026-10-28T22:54:03.321587</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T17:16:09.246562</t>
+          <t>2026-10-28T22:54:03.321576</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28T17:16:09.246557</t>
+          <t>2026-10-28T22:54:03.321563</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1183,7 +1183,7 @@
       <c r="I8" s="2" t="inlineStr"/>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T17:16:09.246552</t>
+          <t>2026-10-28T22:26:00.808636</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       <c r="I9" s="4" t="inlineStr"/>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28T17:16:09.246546</t>
+          <t>2026-10-28T22:26:00.808630</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -1281,7 +1281,7 @@
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T17:16:09.246523</t>
+          <t>2026-10-28T22:54:03.321523</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       <c r="I11" s="4" t="inlineStr"/>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28T17:16:09.245612</t>
+          <t>2026-10-28T22:54:03.319933</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28T17:16:09.267842</t>
+          <t>2026-10-28T22:54:03.345638</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T17:16:09.268646</t>
+          <t>2026-10-28T22:54:03.348489</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28T17:16:09.268667</t>
+          <t>2026-10-28T22:54:03.348541</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T17:16:09.268672</t>
+          <t>2026-10-28T22:54:03.348557</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28T17:16:09.268677</t>
+          <t>2026-10-28T22:54:03.348571</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T17:16:09.268682</t>
+          <t>2026-10-28T22:54:03.348583</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28T17:16:09.268689</t>
+          <t>2026-10-28T22:54:03.348601</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T17:16:09.268693</t>
+          <t>2026-10-28T22:54:03.348613</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1842,7 +1842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5154,6 +5154,43 @@
       <c r="G91" s="4" t="inlineStr">
         <is>
           <t>2026-10-28T17:16:09.232816</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="22" customHeight="1">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1793201576100</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 28 Oct]</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T21:02:58.038864</t>
         </is>
       </c>
     </row>
@@ -5180,8 +5217,8 @@
     <col width="45" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
     <col width="23" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
@@ -5310,17 +5347,17 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>₹21 Lakhs</t>
+          <t>Γé╣21 Lakhs</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>₹21L - ₹48L</t>
+          <t>Γé╣21L - Γé╣48L</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>₹4,200/sq.ft</t>
+          <t>Γé╣4,200/sq.ft</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -5392,17 +5429,17 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>₹23 Lakhs</t>
+          <t>Γé╣23 Lakhs</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>₹23L - ₹42L</t>
+          <t>Γé╣23L - Γé╣42L</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>₹4,100/sq.ft</t>
+          <t>Γé╣4,100/sq.ft</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -5474,17 +5511,17 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>₹18 Lakhs</t>
+          <t>Γé╣18 Lakhs</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>₹18L - ₹27L</t>
+          <t>Γé╣18L - Γé╣27L</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>₹3,900/sq.ft</t>
+          <t>Γé╣3,900/sq.ft</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -5556,17 +5593,17 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>₹28 Lakhs</t>
+          <t>Γé╣28 Lakhs</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>₹28L - ₹65L</t>
+          <t>Γé╣28L - Γé╣65L</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>₹4,600/sq.ft</t>
+          <t>Γé╣4,600/sq.ft</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -5638,17 +5675,17 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>₹34 Lakhs</t>
+          <t>Γé╣34 Lakhs</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>₹34L - ₹68L</t>
+          <t>Γé╣34L - Γé╣68L</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>₹5,200/sq.ft</t>
+          <t>Γé╣5,200/sq.ft</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -5720,17 +5757,17 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>₹32 Lakhs</t>
+          <t>Γé╣32 Lakhs</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>₹32L - ₹62L</t>
+          <t>Γé╣32L - Γé╣62L</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>₹4,800/sq.ft</t>
+          <t>Γé╣4,800/sq.ft</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -5802,17 +5839,17 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>₹19 Lakhs</t>
+          <t>Γé╣19 Lakhs</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>₹19L - ₹38L</t>
+          <t>Γé╣19L - Γé╣38L</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>₹3,900/sq.ft</t>
+          <t>Γé╣3,900/sq.ft</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -5884,17 +5921,17 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>₹27 Lakhs</t>
+          <t>Γé╣27 Lakhs</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>₹27L - ₹48L</t>
+          <t>Γé╣27L - Γé╣48L</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>₹4,400/sq.ft</t>
+          <t>Γé╣4,400/sq.ft</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -5966,17 +6003,17 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>₹24 Lakhs</t>
+          <t>Γé╣24 Lakhs</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>₹24L - ₹42L</t>
+          <t>Γé╣24L - Γé╣42L</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>₹4,000/sq.ft</t>
+          <t>Γé╣4,000/sq.ft</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -6048,17 +6085,17 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>₹29 Lakhs</t>
+          <t>Γé╣29 Lakhs</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>₹29L - ₹49L</t>
+          <t>Γé╣29L - Γé╣49L</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>₹4,500/sq.ft</t>
+          <t>Γé╣4,500/sq.ft</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -6130,17 +6167,17 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>₹31 Lakhs</t>
+          <t>Γé╣31 Lakhs</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>₹31L - ₹52L</t>
+          <t>Γé╣31L - Γé╣52L</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>₹4,700/sq.ft</t>
+          <t>Γé╣4,700/sq.ft</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -6212,17 +6249,17 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>₹30 Lakhs</t>
+          <t>Γé╣30 Lakhs</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>₹30L - ₹54L</t>
+          <t>Γé╣30L - Γé╣54L</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>₹4,650/sq.ft</t>
+          <t>Γé╣4,650/sq.ft</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
@@ -6294,17 +6331,17 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>₹26 Lakhs</t>
+          <t>Γé╣26 Lakhs</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>₹26L - ₹45L</t>
+          <t>Γé╣26L - Γé╣45L</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>₹4,500/sq.ft</t>
+          <t>Γé╣4,500/sq.ft</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -6376,17 +6413,17 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>₹22 Lakhs</t>
+          <t>Γé╣22 Lakhs</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>₹22L - ₹48L</t>
+          <t>Γé╣22L - Γé╣48L</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>₹4,100/sq.ft</t>
+          <t>Γé╣4,100/sq.ft</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
@@ -6458,17 +6495,17 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>₹18 Lakhs</t>
+          <t>Γé╣18 Lakhs</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>₹18L - ₹34L</t>
+          <t>Γé╣18L - Γé╣34L</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>₹3,900/sq.ft</t>
+          <t>Γé╣3,900/sq.ft</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -6540,17 +6577,17 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>₹25 Lakhs</t>
+          <t>Γé╣25 Lakhs</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>₹25L - ₹44L</t>
+          <t>Γé╣25L - Γé╣44L</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>₹4,250/sq.ft</t>
+          <t>Γé╣4,250/sq.ft</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -6622,17 +6659,17 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>₹19 Lakhs</t>
+          <t>Γé╣19 Lakhs</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>₹19L - ₹32L</t>
+          <t>Γé╣19L - Γé╣32L</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>₹3,750/sq.ft</t>
+          <t>Γé╣3,750/sq.ft</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -6704,17 +6741,17 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>₹23 Lakhs</t>
+          <t>Γé╣23 Lakhs</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>₹23L - ₹41L</t>
+          <t>Γé╣23L - Γé╣41L</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>₹4,000/sq.ft</t>
+          <t>Γé╣4,000/sq.ft</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
@@ -6786,17 +6823,17 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>₹21 Lakhs</t>
+          <t>Γé╣21 Lakhs</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>₹21L - ₹37L</t>
+          <t>Γé╣21L - Γé╣37L</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>₹3,850/sq.ft</t>
+          <t>Γé╣3,850/sq.ft</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -6868,17 +6905,17 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>₹24 Lakhs</t>
+          <t>Γé╣24 Lakhs</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>₹24L - ₹40L</t>
+          <t>Γé╣24L - Γé╣40L</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>₹4,100/sq.ft</t>
+          <t>Γé╣4,100/sq.ft</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -6950,17 +6987,17 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>₹34 Lakhs</t>
+          <t>Γé╣34 Lakhs</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>₹34L - ₹65L</t>
+          <t>Γé╣34L - Γé╣65L</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>₹5,800/sq.ft</t>
+          <t>Γé╣5,800/sq.ft</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -7032,17 +7069,17 @@
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>₹42 Lakhs</t>
+          <t>Γé╣42 Lakhs</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>₹42L - ₹78L</t>
+          <t>Γé╣42L - Γé╣78L</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>₹6,100/sq.ft</t>
+          <t>Γé╣6,100/sq.ft</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
@@ -7114,17 +7151,17 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>₹28 Lakhs</t>
+          <t>Γé╣28 Lakhs</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>₹28L - ₹48L</t>
+          <t>Γé╣28L - Γé╣48L</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>₹5,000/sq.ft</t>
+          <t>Γé╣5,000/sq.ft</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -7196,17 +7233,17 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>₹48 Lakhs</t>
+          <t>Γé╣48 Lakhs</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>₹48L - ₹82L</t>
+          <t>Γé╣48L - Γé╣82L</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>₹5,900/sq.ft</t>
+          <t>Γé╣5,900/sq.ft</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -7278,17 +7315,17 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>₹29 Lakhs</t>
+          <t>Γé╣29 Lakhs</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>₹29L - ₹51L</t>
+          <t>Γé╣29L - Γé╣51L</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>₹5,100/sq.ft</t>
+          <t>Γé╣5,100/sq.ft</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -7360,17 +7397,17 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>₹26 Lakhs</t>
+          <t>Γé╣26 Lakhs</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>₹26L - ₹46L</t>
+          <t>Γé╣26L - Γé╣46L</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>₹4,900/sq.ft</t>
+          <t>Γé╣4,900/sq.ft</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
@@ -7442,17 +7479,17 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>₹45 Lakhs</t>
+          <t>Γé╣45 Lakhs</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>₹45L - ₹75L</t>
+          <t>Γé╣45L - Γé╣75L</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>₹5,700/sq.ft</t>
+          <t>Γé╣5,700/sq.ft</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -7524,17 +7561,17 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>₹27 Lakhs</t>
+          <t>Γé╣27 Lakhs</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>₹27L - ₹47L</t>
+          <t>Γé╣27L - Γé╣47L</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>₹4,850/sq.ft</t>
+          <t>Γé╣4,850/sq.ft</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
@@ -7606,17 +7643,17 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>₹31 Lakhs</t>
+          <t>Γé╣31 Lakhs</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>₹31L - ₹53L</t>
+          <t>Γé╣31L - Γé╣53L</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>₹5,200/sq.ft</t>
+          <t>Γé╣5,200/sq.ft</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -7688,17 +7725,17 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>₹28 Lakhs</t>
+          <t>Γé╣28 Lakhs</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>₹28L - ₹49L</t>
+          <t>Γé╣28L - Γé╣49L</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>₹5,050/sq.ft</t>
+          <t>Γé╣5,050/sq.ft</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
@@ -7770,17 +7807,17 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>₹82 Lakhs</t>
+          <t>Γé╣82 Lakhs</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>₹82L - ₹1.45 Cr</t>
+          <t>Γé╣82L - Γé╣1.45 Cr</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>₹7,600/sq.ft</t>
+          <t>Γé╣7,600/sq.ft</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -7852,17 +7889,17 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>₹58 Lakhs</t>
+          <t>Γé╣58 Lakhs</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>₹58L - ₹92L</t>
+          <t>Γé╣58L - Γé╣92L</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>₹7,200/sq.ft</t>
+          <t>Γé╣7,200/sq.ft</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
@@ -7934,17 +7971,17 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>₹88 Lakhs</t>
+          <t>Γé╣88 Lakhs</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>₹88L - ₹1.65 Cr</t>
+          <t>Γé╣88L - Γé╣1.65 Cr</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>₹7,500/sq.ft</t>
+          <t>Γé╣7,500/sq.ft</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -8016,17 +8053,17 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>₹78 Lakhs</t>
+          <t>Γé╣78 Lakhs</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>₹78L - ₹1.28 Cr</t>
+          <t>Γé╣78L - Γé╣1.28 Cr</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>₹7,300/sq.ft</t>
+          <t>Γé╣7,300/sq.ft</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
@@ -8098,17 +8135,17 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>₹52 Lakhs</t>
+          <t>Γé╣52 Lakhs</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>₹52L - ₹1.15 Cr</t>
+          <t>Γé╣52L - Γé╣1.15 Cr</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>₹6,800/sq.ft</t>
+          <t>Γé╣6,800/sq.ft</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -8180,17 +8217,17 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>₹65 Lakhs</t>
+          <t>Γé╣65 Lakhs</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>₹65L - ₹1.05 Cr</t>
+          <t>Γé╣65L - Γé╣1.05 Cr</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>₹6,900/sq.ft</t>
+          <t>Γé╣6,900/sq.ft</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
@@ -8262,17 +8299,17 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>₹35 Lakhs</t>
+          <t>Γé╣35 Lakhs</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>₹35L - ₹68L</t>
+          <t>Γé╣35L - Γé╣68L</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>₹5,400/sq.ft</t>
+          <t>Γé╣5,400/sq.ft</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -8344,17 +8381,17 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>₹49 Lakhs</t>
+          <t>Γé╣49 Lakhs</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>₹49L - ₹1.20 Cr</t>
+          <t>Γé╣49L - Γé╣1.20 Cr</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>₹7,100/sq.ft</t>
+          <t>Γé╣7,100/sq.ft</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
@@ -8426,17 +8463,17 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>₹38 Lakhs</t>
+          <t>Γé╣38 Lakhs</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>₹38L - ₹62L</t>
+          <t>Γé╣38L - Γé╣62L</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>₹5,500/sq.ft</t>
+          <t>Γé╣5,500/sq.ft</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -8508,17 +8545,17 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>₹72 Lakhs</t>
+          <t>Γé╣72 Lakhs</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>₹72L - ₹1.35 Cr</t>
+          <t>Γé╣72L - Γé╣1.35 Cr</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>₹6,800/sq.ft</t>
+          <t>Γé╣6,800/sq.ft</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
@@ -8590,17 +8627,17 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>₹36 Lakhs</t>
+          <t>Γé╣36 Lakhs</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>₹36L - ₹58L</t>
+          <t>Γé╣36L - Γé╣58L</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>₹5,300/sq.ft</t>
+          <t>Γé╣5,300/sq.ft</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -8672,17 +8709,17 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>₹33 Lakhs</t>
+          <t>Γé╣33 Lakhs</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>₹33L - ₹54L</t>
+          <t>Γé╣33L - Γé╣54L</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>₹5,100/sq.ft</t>
+          <t>Γé╣5,100/sq.ft</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
@@ -8754,17 +8791,17 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>₹28 Lakhs</t>
+          <t>Γé╣28 Lakhs</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>₹28L - ₹48L</t>
+          <t>Γé╣28L - Γé╣48L</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>₹4,600/sq.ft</t>
+          <t>Γé╣4,600/sq.ft</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -8836,17 +8873,17 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>₹27 Lakhs</t>
+          <t>Γé╣27 Lakhs</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>₹27L - ₹45L</t>
+          <t>Γé╣27L - Γé╣45L</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>₹4,500/sq.ft</t>
+          <t>Γé╣4,500/sq.ft</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
@@ -8918,17 +8955,17 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>₹44 Lakhs</t>
+          <t>Γé╣44 Lakhs</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>₹44L - ₹72L</t>
+          <t>Γé╣44L - Γé╣72L</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>₹6,400/sq.ft</t>
+          <t>Γé╣6,400/sq.ft</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -9000,17 +9037,17 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>₹62 Lakhs</t>
+          <t>Γé╣62 Lakhs</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>₹62L - ₹98L</t>
+          <t>Γé╣62L - Γé╣98L</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>₹6,700/sq.ft</t>
+          <t>Γé╣6,700/sq.ft</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
@@ -9082,17 +9119,17 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>₹38 Lakhs</t>
+          <t>Γé╣38 Lakhs</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>₹38L - ₹95L</t>
+          <t>Γé╣38L - Γé╣95L</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>₹6,200/sq.ft</t>
+          <t>Γé╣6,200/sq.ft</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -9164,17 +9201,17 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>₹42 Lakhs</t>
+          <t>Γé╣42 Lakhs</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>₹42L - ₹88L</t>
+          <t>Γé╣42L - Γé╣88L</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>₹6,500/sq.ft</t>
+          <t>Γé╣6,500/sq.ft</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
@@ -9246,17 +9283,17 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>₹24 Lakhs</t>
+          <t>Γé╣24 Lakhs</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>₹24L - ₹48L</t>
+          <t>Γé╣24L - Γé╣48L</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>₹5,800/sq.ft</t>
+          <t>Γé╣5,800/sq.ft</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -9328,17 +9365,17 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>₹48 Lakhs</t>
+          <t>Γé╣48 Lakhs</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>₹48L - ₹78L</t>
+          <t>Γé╣48L - Γé╣78L</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>₹6,900/sq.ft</t>
+          <t>Γé╣6,900/sq.ft</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
@@ -9410,17 +9447,17 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>₹36 Lakhs</t>
+          <t>Γé╣36 Lakhs</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>₹36L - ₹56L</t>
+          <t>Γé╣36L - Γé╣56L</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>₹6,300/sq.ft</t>
+          <t>Γé╣6,300/sq.ft</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -9492,17 +9529,17 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>₹68 Lakhs</t>
+          <t>Γé╣68 Lakhs</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>₹68L - ₹1.10 Cr</t>
+          <t>Γé╣68L - Γé╣1.10 Cr</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>₹7,200/sq.ft</t>
+          <t>Γé╣7,200/sq.ft</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
@@ -9574,17 +9611,17 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>₹45 Lakhs</t>
+          <t>Γé╣45 Lakhs</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>₹45L - ₹78L</t>
+          <t>Γé╣45L - Γé╣78L</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>₹6,600/sq.ft</t>
+          <t>Γé╣6,600/sq.ft</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -9656,17 +9693,17 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>₹52 Lakhs</t>
+          <t>Γé╣52 Lakhs</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>₹52L - ₹85L</t>
+          <t>Γé╣52L - Γé╣85L</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>₹7,800/sq.ft</t>
+          <t>Γé╣7,800/sq.ft</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
@@ -9738,17 +9775,17 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>₹39 Lakhs</t>
+          <t>Γé╣39 Lakhs</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>₹39L - ₹85L</t>
+          <t>Γé╣39L - Γé╣85L</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>₹6,100/sq.ft</t>
+          <t>Γé╣6,100/sq.ft</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -9820,17 +9857,17 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>₹46 Lakhs</t>
+          <t>Γé╣46 Lakhs</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>₹46L - ₹74L</t>
+          <t>Γé╣46L - Γé╣74L</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>₹6,800/sq.ft</t>
+          <t>Γé╣6,800/sq.ft</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
@@ -9902,17 +9939,17 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>₹85 Lakhs</t>
+          <t>Γé╣85 Lakhs</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>₹85L - ₹3.50 Cr</t>
+          <t>Γé╣85L - Γé╣3.50 Cr</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>₹15,500/sq.ft</t>
+          <t>Γé╣15,500/sq.ft</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -9954,7 +9991,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Lodha Amāra</t>
+          <t>Lodha Am─üra</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -9984,17 +10021,17 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>₹75 Lakhs</t>
+          <t>Γé╣75 Lakhs</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>₹75L - ₹1.85 Cr</t>
+          <t>Γé╣75L - Γé╣1.85 Cr</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>₹14,200/sq.ft</t>
+          <t>Γé╣14,200/sq.ft</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
@@ -10066,17 +10103,17 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>₹64 Lakhs</t>
+          <t>Γé╣64 Lakhs</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>₹64L - ₹1.45 Cr</t>
+          <t>Γé╣64L - Γé╣1.45 Cr</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>₹12,800/sq.ft</t>
+          <t>Γé╣12,800/sq.ft</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -10148,17 +10185,17 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>₹98 Lakhs</t>
+          <t>Γé╣98 Lakhs</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>₹98L - ₹1.75 Cr</t>
+          <t>Γé╣98L - Γé╣1.75 Cr</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>₹14,800/sq.ft</t>
+          <t>Γé╣14,800/sq.ft</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
@@ -10230,17 +10267,17 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>₹92 Lakhs</t>
+          <t>Γé╣92 Lakhs</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>₹92L - ₹1.35 Cr</t>
+          <t>Γé╣92L - Γé╣1.35 Cr</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>₹14,900/sq.ft</t>
+          <t>Γé╣14,900/sq.ft</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -10312,17 +10349,17 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>₹88 Lakhs</t>
+          <t>Γé╣88 Lakhs</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>₹88L - ₹2.40 Cr</t>
+          <t>Γé╣88L - Γé╣2.40 Cr</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>₹15,200/sq.ft</t>
+          <t>Γé╣15,200/sq.ft</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
@@ -10394,17 +10431,17 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>₹78 Lakhs</t>
+          <t>Γé╣78 Lakhs</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>₹78L - ₹1.65 Cr</t>
+          <t>Γé╣78L - Γé╣1.65 Cr</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>₹14,100/sq.ft</t>
+          <t>Γé╣14,100/sq.ft</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -10476,17 +10513,17 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>₹82 Lakhs</t>
+          <t>Γé╣82 Lakhs</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>₹82L - ₹1.85 Cr</t>
+          <t>Γé╣82L - Γé╣1.85 Cr</t>
         </is>
       </c>
       <c r="J65" s="4" t="inlineStr">
         <is>
-          <t>₹15,100/sq.ft</t>
+          <t>Γé╣15,100/sq.ft</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
@@ -10558,17 +10595,17 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>₹56 Lakhs</t>
+          <t>Γé╣56 Lakhs</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>₹56L - ₹92L</t>
+          <t>Γé╣56L - Γé╣92L</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>₹11,500/sq.ft</t>
+          <t>Γé╣11,500/sq.ft</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -10640,17 +10677,17 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>₹79 Lakhs</t>
+          <t>Γé╣79 Lakhs</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>₹79L - ₹1.35 Cr</t>
+          <t>Γé╣79L - Γé╣1.35 Cr</t>
         </is>
       </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
-          <t>₹15,400/sq.ft</t>
+          <t>Γé╣15,400/sq.ft</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
@@ -10722,17 +10759,17 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>₹48 Lakhs</t>
+          <t>Γé╣48 Lakhs</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>₹48L - ₹78L</t>
+          <t>Γé╣48L - Γé╣78L</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>₹11,200/sq.ft</t>
+          <t>Γé╣11,200/sq.ft</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -10804,17 +10841,17 @@
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>₹1.45 Cr</t>
+          <t>Γé╣1.45 Cr</t>
         </is>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>₹1.45 Cr - ₹3.80 Cr</t>
+          <t>Γé╣1.45 Cr - Γé╣3.80 Cr</t>
         </is>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>₹17,500/sq.ft</t>
+          <t>Γé╣17,500/sq.ft</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
@@ -10886,17 +10923,17 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>₹1.35 Cr</t>
+          <t>Γé╣1.35 Cr</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>₹1.35 Cr - ₹2.65 Cr</t>
+          <t>Γé╣1.35 Cr - Γé╣2.65 Cr</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>₹16,200/sq.ft</t>
+          <t>Γé╣16,200/sq.ft</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -10968,17 +11005,17 @@
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>₹68 Lakhs</t>
+          <t>Γé╣68 Lakhs</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>₹68L - ₹1.25 Cr</t>
+          <t>Γé╣68L - Γé╣1.25 Cr</t>
         </is>
       </c>
       <c r="J71" s="4" t="inlineStr">
         <is>
-          <t>₹13,800/sq.ft</t>
+          <t>Γé╣13,800/sq.ft</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
@@ -11050,17 +11087,17 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>₹69 Lakhs</t>
+          <t>Γé╣69 Lakhs</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>₹69L - ₹1.55 Cr</t>
+          <t>Γé╣69L - Γé╣1.55 Cr</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>₹13,200/sq.ft</t>
+          <t>Γé╣13,200/sq.ft</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -11132,17 +11169,17 @@
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>₹38 Lakhs</t>
+          <t>Γé╣38 Lakhs</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>₹38L - ₹64L</t>
+          <t>Γé╣38L - Γé╣64L</t>
         </is>
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>₹6,400/sq.ft</t>
+          <t>Γé╣6,400/sq.ft</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
@@ -11214,17 +11251,17 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>₹3.20 Cr</t>
+          <t>Γé╣3.20 Cr</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>₹3.2 Cr - ₹5.8 Cr</t>
+          <t>Γé╣3.2 Cr - Γé╣5.8 Cr</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>₹27,500/sq.ft</t>
+          <t>Γé╣27,500/sq.ft</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -11296,17 +11333,17 @@
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>₹98 Lakhs</t>
+          <t>Γé╣98 Lakhs</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>₹98L - ₹2.10 Cr</t>
+          <t>Γé╣98L - Γé╣2.10 Cr</t>
         </is>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>₹18,200/sq.ft</t>
+          <t>Γé╣18,200/sq.ft</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
@@ -11378,17 +11415,17 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>₹3.60 Cr</t>
+          <t>Γé╣3.60 Cr</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>₹3.6 Cr - ₹6.8 Cr</t>
+          <t>Γé╣3.6 Cr - Γé╣6.8 Cr</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>₹28,500/sq.ft</t>
+          <t>Γé╣28,500/sq.ft</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -11460,17 +11497,17 @@
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>₹1.85 Cr</t>
+          <t>Γé╣1.85 Cr</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>₹1.85 Cr - ₹3.20 Cr</t>
+          <t>Γé╣1.85 Cr - Γé╣3.20 Cr</t>
         </is>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>₹21,800/sq.ft</t>
+          <t>Γé╣21,800/sq.ft</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
@@ -11542,17 +11579,17 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>₹2.45 Cr</t>
+          <t>Γé╣2.45 Cr</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>₹2.45 Cr - ₹5.20 Cr</t>
+          <t>Γé╣2.45 Cr - Γé╣5.20 Cr</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>₹26,000/sq.ft</t>
+          <t>Γé╣26,000/sq.ft</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -11624,17 +11661,17 @@
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>₹1.95 Cr</t>
+          <t>Γé╣1.95 Cr</t>
         </is>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>₹1.95 Cr - ₹4.50 Cr</t>
+          <t>Γé╣1.95 Cr - Γé╣4.50 Cr</t>
         </is>
       </c>
       <c r="J79" s="4" t="inlineStr">
         <is>
-          <t>₹22,500/sq.ft</t>
+          <t>Γé╣22,500/sq.ft</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
@@ -11706,17 +11743,17 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>₹1.80 Cr</t>
+          <t>Γé╣1.80 Cr</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>₹1.80 Cr - ₹4.20 Cr</t>
+          <t>Γé╣1.80 Cr - Γé╣4.20 Cr</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>₹20,500/sq.ft</t>
+          <t>Γé╣20,500/sq.ft</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -11788,17 +11825,17 @@
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>₹4.80 Cr</t>
+          <t>Γé╣4.80 Cr</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>₹4.8 Cr - ₹9.5 Cr</t>
+          <t>Γé╣4.8 Cr - Γé╣9.5 Cr</t>
         </is>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>₹38,000/sq.ft</t>
+          <t>Γé╣38,000/sq.ft</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
@@ -11870,17 +11907,17 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>₹68 Lakhs</t>
+          <t>Γé╣68 Lakhs</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>₹68L - ₹1.45 Cr</t>
+          <t>Γé╣68L - Γé╣1.45 Cr</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>₹13,200/sq.ft</t>
+          <t>Γé╣13,200/sq.ft</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -11952,17 +11989,17 @@
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>₹59 Lakhs</t>
+          <t>Γé╣59 Lakhs</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>₹59L - ₹1.28 Cr</t>
+          <t>Γé╣59L - Γé╣1.28 Cr</t>
         </is>
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>₹12,400/sq.ft</t>
+          <t>Γé╣12,400/sq.ft</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
@@ -12034,17 +12071,17 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>₹72 Lakhs</t>
+          <t>Γé╣72 Lakhs</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>₹72L - ₹1.22 Cr</t>
+          <t>Γé╣72L - Γé╣1.22 Cr</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>₹14,500/sq.ft</t>
+          <t>Γé╣14,500/sq.ft</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -12116,17 +12153,17 @@
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>₹1.75 Cr</t>
+          <t>Γé╣1.75 Cr</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>₹1.75 Cr - ₹3.10 Cr</t>
+          <t>Γé╣1.75 Cr - Γé╣3.10 Cr</t>
         </is>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>₹22,000/sq.ft</t>
+          <t>Γé╣22,000/sq.ft</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
@@ -12198,17 +12235,17 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>₹2.85 Cr</t>
+          <t>Γé╣2.85 Cr</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>₹2.85 Cr - ₹6.50 Cr</t>
+          <t>Γé╣2.85 Cr - Γé╣6.50 Cr</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>₹28,000/sq.ft</t>
+          <t>Γé╣28,000/sq.ft</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -12280,17 +12317,17 @@
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>₹85 Lakhs</t>
+          <t>Γé╣85 Lakhs</t>
         </is>
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>₹85L - ₹1.45 Cr</t>
+          <t>Γé╣85L - Γé╣1.45 Cr</t>
         </is>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>₹17,800/sq.ft</t>
+          <t>Γé╣17,800/sq.ft</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
@@ -12362,17 +12399,17 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>₹4.50 Cr</t>
+          <t>Γé╣4.50 Cr</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>₹4.5 Cr - ₹16.0 Cr</t>
+          <t>Γé╣4.5 Cr - Γé╣16.0 Cr</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>₹42,000/sq.ft</t>
+          <t>Γé╣42,000/sq.ft</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -12444,17 +12481,17 @@
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>₹2.95 Cr</t>
+          <t>Γé╣2.95 Cr</t>
         </is>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>₹2.95 Cr - ₹8.50 Cr</t>
+          <t>Γé╣2.95 Cr - Γé╣8.50 Cr</t>
         </is>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>₹34,000/sq.ft</t>
+          <t>Γé╣34,000/sq.ft</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
@@ -12526,17 +12563,17 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>₹1.65 Cr</t>
+          <t>Γé╣1.65 Cr</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>₹1.65 Cr - ₹3.80 Cr</t>
+          <t>Γé╣1.65 Cr - Γé╣3.80 Cr</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>₹24,500/sq.ft</t>
+          <t>Γé╣24,500/sq.ft</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -12608,17 +12645,17 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>₹1.48 Cr</t>
+          <t>Γé╣1.48 Cr</t>
         </is>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>₹1.48 Cr - ₹2.65 Cr</t>
+          <t>Γé╣1.48 Cr - Γé╣2.65 Cr</t>
         </is>
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>₹19,800/sq.ft</t>
+          <t>Γé╣19,800/sq.ft</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
@@ -12690,17 +12727,17 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>₹98 Lakhs</t>
+          <t>Γé╣98 Lakhs</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>₹98L - ₹2.20 Cr</t>
+          <t>Γé╣98L - Γé╣2.20 Cr</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>₹18,500/sq.ft</t>
+          <t>Γé╣18,500/sq.ft</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -12772,17 +12809,17 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>₹1.65 Cr</t>
+          <t>Γé╣1.65 Cr</t>
         </is>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>₹1.65 Cr - ₹4.50 Cr</t>
+          <t>Γé╣1.65 Cr - Γé╣4.50 Cr</t>
         </is>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>₹24,000/sq.ft</t>
+          <t>Γé╣24,000/sq.ft</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
@@ -12854,17 +12891,17 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>₹92 Lakhs</t>
+          <t>Γé╣92 Lakhs</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>₹92L - ₹2.10 Cr</t>
+          <t>Γé╣92L - Γé╣2.10 Cr</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>₹17,800/sq.ft</t>
+          <t>Γé╣17,800/sq.ft</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -12936,17 +12973,17 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>₹1.85 Cr</t>
+          <t>Γé╣1.85 Cr</t>
         </is>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>₹1.85 Cr - ₹3.90 Cr</t>
+          <t>Γé╣1.85 Cr - Γé╣3.90 Cr</t>
         </is>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>₹22,500/sq.ft</t>
+          <t>Γé╣22,500/sq.ft</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
@@ -13018,17 +13055,17 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>₹1.35 Cr</t>
+          <t>Γé╣1.35 Cr</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>₹1.35 Cr - ₹2.35 Cr</t>
+          <t>Γé╣1.35 Cr - Γé╣2.35 Cr</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>₹20,500/sq.ft</t>
+          <t>Γé╣20,500/sq.ft</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -13100,17 +13137,17 @@
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>₹3.10 Cr</t>
+          <t>Γé╣3.10 Cr</t>
         </is>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>₹3.1 Cr - ₹6.8 Cr</t>
+          <t>Γé╣3.1 Cr - Γé╣6.8 Cr</t>
         </is>
       </c>
       <c r="J97" s="4" t="inlineStr">
         <is>
-          <t>₹33,000/sq.ft</t>
+          <t>Γé╣33,000/sq.ft</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
@@ -13182,17 +13219,17 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>₹6.50 Cr</t>
+          <t>Γé╣6.50 Cr</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>₹6.5 Cr - ₹14.0 Cr</t>
+          <t>Γé╣6.5 Cr - Γé╣14.0 Cr</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>₹45,000/sq.ft</t>
+          <t>Γé╣45,000/sq.ft</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -13264,17 +13301,17 @@
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>₹1.72 Cr</t>
+          <t>Γé╣1.72 Cr</t>
         </is>
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>₹1.72 Cr - ₹2.95 Cr</t>
+          <t>Γé╣1.72 Cr - Γé╣2.95 Cr</t>
         </is>
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>₹21,000/sq.ft</t>
+          <t>Γé╣21,000/sq.ft</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
@@ -13346,17 +13383,17 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>₹1.55 Cr</t>
+          <t>Γé╣1.55 Cr</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>₹1.55 Cr - ₹2.85 Cr</t>
+          <t>Γé╣1.55 Cr - Γé╣2.85 Cr</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>₹23,000/sq.ft</t>
+          <t>Γé╣23,000/sq.ft</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -13428,17 +13465,17 @@
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>₹8.50 Cr</t>
+          <t>Γé╣8.50 Cr</t>
         </is>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>₹8.5 Cr - ₹18.0 Cr</t>
+          <t>Γé╣8.5 Cr - Γé╣18.0 Cr</t>
         </is>
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>₹48,000/sq.ft</t>
+          <t>Γé╣48,000/sq.ft</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
@@ -13510,17 +13547,17 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>₹9.80 Cr</t>
+          <t>Γé╣9.80 Cr</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>₹9.8 Cr - ₹25.0 Cr</t>
+          <t>Γé╣9.8 Cr - Γé╣25.0 Cr</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>₹52,000/sq.ft</t>
+          <t>Γé╣52,000/sq.ft</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -13592,17 +13629,17 @@
       </c>
       <c r="H103" s="4" t="inlineStr">
         <is>
-          <t>₹2.90 Cr</t>
+          <t>Γé╣2.90 Cr</t>
         </is>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>₹2.9 Cr - ₹5.4 Cr</t>
+          <t>Γé╣2.9 Cr - Γé╣5.4 Cr</t>
         </is>
       </c>
       <c r="J103" s="4" t="inlineStr">
         <is>
-          <t>₹36,000/sq.ft</t>
+          <t>Γé╣36,000/sq.ft</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr">
@@ -13674,17 +13711,17 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>₹48 Lakhs</t>
+          <t>Γé╣48 Lakhs</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>₹48L - ₹85L</t>
+          <t>Γé╣48L - Γé╣85L</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>₹7,200/sq.ft</t>
+          <t>Γé╣7,200/sq.ft</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -13756,17 +13793,17 @@
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>₹68 Lakhs</t>
+          <t>Γé╣68 Lakhs</t>
         </is>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>₹68L - ₹1.75 Cr</t>
+          <t>Γé╣68L - Γé╣1.75 Cr</t>
         </is>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>₹8,400/sq.ft</t>
+          <t>Γé╣8,400/sq.ft</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr">
@@ -13838,17 +13875,17 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>₹32 Lakhs</t>
+          <t>Γé╣32 Lakhs</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>₹32L - ₹65L</t>
+          <t>Γé╣32L - Γé╣65L</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>₹6,100/sq.ft</t>
+          <t>Γé╣6,100/sq.ft</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -13920,17 +13957,17 @@
       </c>
       <c r="H107" s="4" t="inlineStr">
         <is>
-          <t>₹46 Lakhs</t>
+          <t>Γé╣46 Lakhs</t>
         </is>
       </c>
       <c r="I107" s="4" t="inlineStr">
         <is>
-          <t>₹46L - ₹78L</t>
+          <t>Γé╣46L - Γé╣78L</t>
         </is>
       </c>
       <c r="J107" s="4" t="inlineStr">
         <is>
-          <t>₹7,400/sq.ft</t>
+          <t>Γé╣7,400/sq.ft</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
@@ -14002,17 +14039,17 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>₹41 Lakhs</t>
+          <t>Γé╣41 Lakhs</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>₹41L - ₹1.10 Cr</t>
+          <t>Γé╣41L - Γé╣1.10 Cr</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>₹6,600/sq.ft</t>
+          <t>Γé╣6,600/sq.ft</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -14084,17 +14121,17 @@
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>₹1.85 Cr</t>
+          <t>Γé╣1.85 Cr</t>
         </is>
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>₹1.85 Cr - ₹3.80 Cr</t>
+          <t>Γé╣1.85 Cr - Γé╣3.80 Cr</t>
         </is>
       </c>
       <c r="J109" s="4" t="inlineStr">
         <is>
-          <t>₹21,500/sq.ft</t>
+          <t>Γé╣21,500/sq.ft</t>
         </is>
       </c>
       <c r="K109" s="4" t="inlineStr">
@@ -14166,17 +14203,17 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>₹72 Lakhs</t>
+          <t>Γé╣72 Lakhs</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>₹72L - ₹1.60 Cr</t>
+          <t>Γé╣72L - Γé╣1.60 Cr</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>₹9,800/sq.ft</t>
+          <t>Γé╣9,800/sq.ft</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -14248,17 +14285,17 @@
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>₹1.25 Cr</t>
+          <t>Γé╣1.25 Cr</t>
         </is>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>₹1.25 Cr - ₹2.80 Cr</t>
+          <t>Γé╣1.25 Cr - Γé╣2.80 Cr</t>
         </is>
       </c>
       <c r="J111" s="4" t="inlineStr">
         <is>
-          <t>₹12,400/sq.ft</t>
+          <t>Γé╣12,400/sq.ft</t>
         </is>
       </c>
       <c r="K111" s="4" t="inlineStr">
@@ -14330,17 +14367,17 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>₹85 Lakhs</t>
+          <t>Γé╣85 Lakhs</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
         <is>
-          <t>₹85L - ₹1.45 Cr</t>
+          <t>Γé╣85L - Γé╣1.45 Cr</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>₹10,500/sq.ft</t>
+          <t>Γé╣10,500/sq.ft</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -14412,17 +14449,17 @@
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>₹32 Lakhs</t>
+          <t>Γé╣32 Lakhs</t>
         </is>
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>₹32L - ₹56L</t>
+          <t>Γé╣32L - Γé╣56L</t>
         </is>
       </c>
       <c r="J113" s="4" t="inlineStr">
         <is>
-          <t>₹5,800/sq.ft</t>
+          <t>Γé╣5,800/sq.ft</t>
         </is>
       </c>
       <c r="K113" s="4" t="inlineStr">
@@ -14494,17 +14531,17 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>₹78 Lakhs</t>
+          <t>Γé╣78 Lakhs</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>₹78L - ₹1.25 Cr</t>
+          <t>Γé╣78L - Γé╣1.25 Cr</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>₹9,500/sq.ft</t>
+          <t>Γé╣9,500/sq.ft</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -14576,17 +14613,17 @@
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>₹54 Lakhs</t>
+          <t>Γé╣54 Lakhs</t>
         </is>
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>₹54L - ₹86L</t>
+          <t>Γé╣54L - Γé╣86L</t>
         </is>
       </c>
       <c r="J115" s="4" t="inlineStr">
         <is>
-          <t>₹9,200/sq.ft</t>
+          <t>Γé╣9,200/sq.ft</t>
         </is>
       </c>
       <c r="K115" s="4" t="inlineStr">
@@ -14658,17 +14695,17 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>₹34 Lakhs</t>
+          <t>Γé╣34 Lakhs</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>₹34L - ₹58L</t>
+          <t>Γé╣34L - Γé╣58L</t>
         </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>₹5,600/sq.ft</t>
+          <t>Γé╣5,600/sq.ft</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -14740,17 +14777,17 @@
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>₹88 Lakhs</t>
+          <t>Γé╣88 Lakhs</t>
         </is>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>₹88L - ₹1.95 Cr</t>
+          <t>Γé╣88L - Γé╣1.95 Cr</t>
         </is>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>₹14,500/sq.ft</t>
+          <t>Γé╣14,500/sq.ft</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr">
@@ -14822,17 +14859,17 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>₹1.45 Cr</t>
+          <t>Γé╣1.45 Cr</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>₹1.45 Cr - ₹2.60 Cr</t>
+          <t>Γé╣1.45 Cr - Γé╣2.60 Cr</t>
         </is>
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>₹17,800/sq.ft</t>
+          <t>Γé╣17,800/sq.ft</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -14904,17 +14941,17 @@
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>₹38 Lakhs</t>
+          <t>Γé╣38 Lakhs</t>
         </is>
       </c>
       <c r="I119" s="4" t="inlineStr">
         <is>
-          <t>₹38L - ₹68L</t>
+          <t>Γé╣38L - Γé╣68L</t>
         </is>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>₹6,800/sq.ft</t>
+          <t>Γé╣6,800/sq.ft</t>
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr">
@@ -14986,17 +15023,17 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>₹36 Lakhs</t>
+          <t>Γé╣36 Lakhs</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>₹36L - ₹62L</t>
+          <t>Γé╣36L - Γé╣62L</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>₹6,500/sq.ft</t>
+          <t>Γé╣6,500/sq.ft</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -15068,17 +15105,17 @@
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>₹1.65 Cr</t>
+          <t>Γé╣1.65 Cr</t>
         </is>
       </c>
       <c r="I121" s="4" t="inlineStr">
         <is>
-          <t>₹1.65 Cr - ₹3.10 Cr</t>
+          <t>Γé╣1.65 Cr - Γé╣3.10 Cr</t>
         </is>
       </c>
       <c r="J121" s="4" t="inlineStr">
         <is>
-          <t>₹19,200/sq.ft</t>
+          <t>Γé╣19,200/sq.ft</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr">
@@ -15150,17 +15187,17 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>₹65 Lakhs</t>
+          <t>Γé╣65 Lakhs</t>
         </is>
       </c>
       <c r="I122" s="2" t="inlineStr">
         <is>
-          <t>₹65L - ₹1.15 Cr</t>
+          <t>Γé╣65L - Γé╣1.15 Cr</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>₹12,800/sq.ft</t>
+          <t>Γé╣12,800/sq.ft</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -15232,17 +15269,17 @@
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>₹62 Lakhs</t>
+          <t>Γé╣62 Lakhs</t>
         </is>
       </c>
       <c r="I123" s="4" t="inlineStr">
         <is>
-          <t>₹62L - ₹1.05 Cr</t>
+          <t>Γé╣62L - Γé╣1.05 Cr</t>
         </is>
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>₹12,200/sq.ft</t>
+          <t>Γé╣12,200/sq.ft</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr">
@@ -15314,17 +15351,17 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>₹66 Lakhs</t>
+          <t>Γé╣66 Lakhs</t>
         </is>
       </c>
       <c r="I124" s="2" t="inlineStr">
         <is>
-          <t>₹66L - ₹1.12 Cr</t>
+          <t>Γé╣66L - Γé╣1.12 Cr</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>₹12,500/sq.ft</t>
+          <t>Γé╣12,500/sq.ft</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -15396,17 +15433,17 @@
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>₹72 Lakhs</t>
+          <t>Γé╣72 Lakhs</t>
         </is>
       </c>
       <c r="I125" s="4" t="inlineStr">
         <is>
-          <t>₹72L - ₹1.35 Cr</t>
+          <t>Γé╣72L - Γé╣1.35 Cr</t>
         </is>
       </c>
       <c r="J125" s="4" t="inlineStr">
         <is>
-          <t>₹13,500/sq.ft</t>
+          <t>Γé╣13,500/sq.ft</t>
         </is>
       </c>
       <c r="K125" s="4" t="inlineStr">
@@ -15478,17 +15515,17 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>₹58 Lakhs</t>
+          <t>Γé╣58 Lakhs</t>
         </is>
       </c>
       <c r="I126" s="2" t="inlineStr">
         <is>
-          <t>₹58L - ₹95L</t>
+          <t>Γé╣58L - Γé╣95L</t>
         </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>₹11,800/sq.ft</t>
+          <t>Γé╣11,800/sq.ft</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -15560,17 +15597,17 @@
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>₹64 Lakhs</t>
+          <t>Γé╣64 Lakhs</t>
         </is>
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>₹64L - ₹1.08 Cr</t>
+          <t>Γé╣64L - Γé╣1.08 Cr</t>
         </is>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
-          <t>₹12,400/sq.ft</t>
+          <t>Γé╣12,400/sq.ft</t>
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr">
@@ -15642,17 +15679,17 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>₹34 Lakhs</t>
+          <t>Γé╣34 Lakhs</t>
         </is>
       </c>
       <c r="I128" s="2" t="inlineStr">
         <is>
-          <t>₹34L - ₹54L</t>
+          <t>Γé╣34L - Γé╣54L</t>
         </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>₹5,400/sq.ft</t>
+          <t>Γé╣5,400/sq.ft</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -15724,17 +15761,17 @@
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>₹36 Lakhs</t>
+          <t>Γé╣36 Lakhs</t>
         </is>
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>₹36L - ₹62L</t>
+          <t>Γé╣36L - Γé╣62L</t>
         </is>
       </c>
       <c r="J129" s="4" t="inlineStr">
         <is>
-          <t>₹5,600/sq.ft</t>
+          <t>Γé╣5,600/sq.ft</t>
         </is>
       </c>
       <c r="K129" s="4" t="inlineStr">
@@ -15806,17 +15843,17 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>₹32 Lakhs</t>
+          <t>Γé╣32 Lakhs</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>₹32L - ₹52L</t>
+          <t>Γé╣32L - Γé╣52L</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>₹5,800/sq.ft</t>
+          <t>Γé╣5,800/sq.ft</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -15888,17 +15925,17 @@
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>₹68 Lakhs</t>
+          <t>Γé╣68 Lakhs</t>
         </is>
       </c>
       <c r="I131" s="4" t="inlineStr">
         <is>
-          <t>₹68L - ₹1.25 Cr</t>
+          <t>Γé╣68L - Γé╣1.25 Cr</t>
         </is>
       </c>
       <c r="J131" s="4" t="inlineStr">
         <is>
-          <t>₹7,800/sq.ft</t>
+          <t>Γé╣7,800/sq.ft</t>
         </is>
       </c>
       <c r="K131" s="4" t="inlineStr">
@@ -15970,17 +16007,17 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>₹30 Lakhs</t>
+          <t>Γé╣30 Lakhs</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>₹30L - ₹48L</t>
+          <t>Γé╣30L - Γé╣48L</t>
         </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>₹5,100/sq.ft</t>
+          <t>Γé╣5,100/sq.ft</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -16052,17 +16089,17 @@
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>₹33 Lakhs</t>
+          <t>Γé╣33 Lakhs</t>
         </is>
       </c>
       <c r="I133" s="4" t="inlineStr">
         <is>
-          <t>₹33L - ₹54L</t>
+          <t>Γé╣33L - Γé╣54L</t>
         </is>
       </c>
       <c r="J133" s="4" t="inlineStr">
         <is>
-          <t>₹5,300/sq.ft</t>
+          <t>Γé╣5,300/sq.ft</t>
         </is>
       </c>
       <c r="K133" s="4" t="inlineStr">
@@ -16134,17 +16171,17 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>₹26 Lakhs</t>
+          <t>Γé╣26 Lakhs</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>₹26L - ₹42L</t>
+          <t>Γé╣26L - Γé╣42L</t>
         </is>
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>₹4,600/sq.ft</t>
+          <t>Γé╣4,600/sq.ft</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -16216,17 +16253,17 @@
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>₹31 Lakhs</t>
+          <t>Γé╣31 Lakhs</t>
         </is>
       </c>
       <c r="I135" s="4" t="inlineStr">
         <is>
-          <t>₹31L - ₹49L</t>
+          <t>Γé╣31L - Γé╣49L</t>
         </is>
       </c>
       <c r="J135" s="4" t="inlineStr">
         <is>
-          <t>₹5,200/sq.ft</t>
+          <t>Γé╣5,200/sq.ft</t>
         </is>
       </c>
       <c r="K135" s="4" t="inlineStr">
@@ -16298,17 +16335,17 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>₹26 Lakhs</t>
+          <t>Γé╣26 Lakhs</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>₹26L - ₹45L</t>
+          <t>Γé╣26L - Γé╣45L</t>
         </is>
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>₹4,800/sq.ft</t>
+          <t>Γé╣4,800/sq.ft</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -16380,17 +16417,17 @@
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>₹19 Lakhs</t>
+          <t>Γé╣19 Lakhs</t>
         </is>
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>₹19L - ₹36L</t>
+          <t>Γé╣19L - Γé╣36L</t>
         </is>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
-          <t>₹4,200/sq.ft</t>
+          <t>Γé╣4,200/sq.ft</t>
         </is>
       </c>
       <c r="K137" s="4" t="inlineStr">
@@ -16462,17 +16499,17 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>₹24 Lakhs</t>
+          <t>Γé╣24 Lakhs</t>
         </is>
       </c>
       <c r="I138" s="2" t="inlineStr">
         <is>
-          <t>₹24L - ₹41L</t>
+          <t>Γé╣24L - Γé╣41L</t>
         </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>₹4,400/sq.ft</t>
+          <t>Γé╣4,400/sq.ft</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -16544,17 +16581,17 @@
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>₹28 Lakhs</t>
+          <t>Γé╣28 Lakhs</t>
         </is>
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>₹28L - ₹48L</t>
+          <t>Γé╣28L - Γé╣48L</t>
         </is>
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>₹4,900/sq.ft</t>
+          <t>Γé╣4,900/sq.ft</t>
         </is>
       </c>
       <c r="K139" s="4" t="inlineStr">
@@ -16626,17 +16663,17 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>₹23 Lakhs</t>
+          <t>Γé╣23 Lakhs</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>₹23L - ₹39L</t>
+          <t>Γé╣23L - Γé╣39L</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>₹4,300/sq.ft</t>
+          <t>Γé╣4,300/sq.ft</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -16708,17 +16745,17 @@
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>₹27 Lakhs</t>
+          <t>Γé╣27 Lakhs</t>
         </is>
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>₹27L - ₹46L</t>
+          <t>Γé╣27L - Γé╣46L</t>
         </is>
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
-          <t>₹4,600/sq.ft</t>
+          <t>Γé╣4,600/sq.ft</t>
         </is>
       </c>
       <c r="K141" s="4" t="inlineStr">
@@ -16790,17 +16827,17 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>₹15 Lakhs</t>
+          <t>Γé╣15 Lakhs</t>
         </is>
       </c>
       <c r="I142" s="2" t="inlineStr">
         <is>
-          <t>₹15L - ₹32L</t>
+          <t>Γé╣15L - Γé╣32L</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>₹3,400/sq.ft</t>
+          <t>Γé╣3,400/sq.ft</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -16872,17 +16909,17 @@
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>₹16 Lakhs</t>
+          <t>Γé╣16 Lakhs</t>
         </is>
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>₹16L - ₹35L</t>
+          <t>Γé╣16L - Γé╣35L</t>
         </is>
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
-          <t>₹3,500/sq.ft</t>
+          <t>Γé╣3,500/sq.ft</t>
         </is>
       </c>
       <c r="K143" s="4" t="inlineStr">
@@ -16954,17 +16991,17 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>₹14 Lakhs</t>
+          <t>Γé╣14 Lakhs</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>₹14L - ₹28L</t>
+          <t>Γé╣14L - Γé╣28L</t>
         </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>₹3,200/sq.ft</t>
+          <t>Γé╣3,200/sq.ft</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -17036,17 +17073,17 @@
       </c>
       <c r="H145" s="4" t="inlineStr">
         <is>
-          <t>₹17 Lakhs</t>
+          <t>Γé╣17 Lakhs</t>
         </is>
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>₹17L - ₹29L</t>
+          <t>Γé╣17L - Γé╣29L</t>
         </is>
       </c>
       <c r="J145" s="4" t="inlineStr">
         <is>
-          <t>₹3,350/sq.ft</t>
+          <t>Γé╣3,350/sq.ft</t>
         </is>
       </c>
       <c r="K145" s="4" t="inlineStr">
@@ -17118,17 +17155,17 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>₹18 Lakhs</t>
+          <t>Γé╣18 Lakhs</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>₹18L - ₹31L</t>
+          <t>Γé╣18L - Γé╣31L</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>₹3,450/sq.ft</t>
+          <t>Γé╣3,450/sq.ft</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -17200,17 +17237,17 @@
       </c>
       <c r="H147" s="4" t="inlineStr">
         <is>
-          <t>₹15.5 Lakhs</t>
+          <t>Γé╣15.5 Lakhs</t>
         </is>
       </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>₹15.5L - ₹30L</t>
+          <t>Γé╣15.5L - Γé╣30L</t>
         </is>
       </c>
       <c r="J147" s="4" t="inlineStr">
         <is>
-          <t>₹3,300/sq.ft</t>
+          <t>Γé╣3,300/sq.ft</t>
         </is>
       </c>
       <c r="K147" s="4" t="inlineStr">
@@ -17282,17 +17319,17 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>₹14 Lakhs</t>
+          <t>Γé╣14 Lakhs</t>
         </is>
       </c>
       <c r="I148" s="2" t="inlineStr">
         <is>
-          <t>₹14L - ₹28L</t>
+          <t>Γé╣14L - Γé╣28L</t>
         </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>₹3,100/sq.ft</t>
+          <t>Γé╣3,100/sq.ft</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -17364,17 +17401,17 @@
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
-          <t>₹16 Lakhs</t>
+          <t>Γé╣16 Lakhs</t>
         </is>
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>₹16L - ₹26L</t>
+          <t>Γé╣16L - Γé╣26L</t>
         </is>
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
-          <t>₹3,300/sq.ft</t>
+          <t>Γé╣3,300/sq.ft</t>
         </is>
       </c>
       <c r="K149" s="4" t="inlineStr">
@@ -17446,17 +17483,17 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>₹15 Lakhs</t>
+          <t>Γé╣15 Lakhs</t>
         </is>
       </c>
       <c r="I150" s="2" t="inlineStr">
         <is>
-          <t>₹15L - ₹24L</t>
+          <t>Γé╣15L - Γé╣24L</t>
         </is>
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>₹3,200/sq.ft</t>
+          <t>Γé╣3,200/sq.ft</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -17528,17 +17565,17 @@
       </c>
       <c r="H151" s="4" t="inlineStr">
         <is>
-          <t>₹28 Lakhs</t>
+          <t>Γé╣28 Lakhs</t>
         </is>
       </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>₹28L - ₹55L</t>
+          <t>Γé╣28L - Γé╣55L</t>
         </is>
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
-          <t>₹4,200/sq.ft</t>
+          <t>Γé╣4,200/sq.ft</t>
         </is>
       </c>
       <c r="K151" s="4" t="inlineStr">
@@ -17610,17 +17647,17 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>₹31 Lakhs</t>
+          <t>Γé╣31 Lakhs</t>
         </is>
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>₹31L - ₹65L</t>
+          <t>Γé╣31L - Γé╣65L</t>
         </is>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>₹4,400/sq.ft</t>
+          <t>Γé╣4,400/sq.ft</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -17692,17 +17729,17 @@
       </c>
       <c r="H153" s="4" t="inlineStr">
         <is>
-          <t>₹14.5 Lakhs</t>
+          <t>Γé╣14.5 Lakhs</t>
         </is>
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>₹14.5L - ₹23L</t>
+          <t>Γé╣14.5L - Γé╣23L</t>
         </is>
       </c>
       <c r="J153" s="4" t="inlineStr">
         <is>
-          <t>₹3,150/sq.ft</t>
+          <t>Γé╣3,150/sq.ft</t>
         </is>
       </c>
       <c r="K153" s="4" t="inlineStr">
@@ -17774,17 +17811,17 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>₹15 Lakhs</t>
+          <t>Γé╣15 Lakhs</t>
         </is>
       </c>
       <c r="I154" s="2" t="inlineStr">
         <is>
-          <t>₹15L - ₹29L</t>
+          <t>Γé╣15L - Γé╣29L</t>
         </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>₹3,200/sq.ft</t>
+          <t>Γé╣3,200/sq.ft</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -17856,17 +17893,17 @@
       </c>
       <c r="H155" s="4" t="inlineStr">
         <is>
-          <t>₹18 Lakhs</t>
+          <t>Γé╣18 Lakhs</t>
         </is>
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>₹18L - ₹32L</t>
+          <t>Γé╣18L - Γé╣32L</t>
         </is>
       </c>
       <c r="J155" s="4" t="inlineStr">
         <is>
-          <t>₹3,400/sq.ft</t>
+          <t>Γé╣3,400/sq.ft</t>
         </is>
       </c>
       <c r="K155" s="4" t="inlineStr">
@@ -17938,17 +17975,17 @@
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>₹24 Lakhs</t>
+          <t>Γé╣24 Lakhs</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>₹24L - ₹52L</t>
+          <t>Γé╣24L - Γé╣52L</t>
         </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>₹3,800/sq.ft</t>
+          <t>Γé╣3,800/sq.ft</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -18020,17 +18057,17 @@
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>₹14 Lakhs</t>
+          <t>Γé╣14 Lakhs</t>
         </is>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>₹14L - ₹23L</t>
+          <t>Γé╣14L - Γé╣23L</t>
         </is>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
-          <t>₹3,150/sq.ft</t>
+          <t>Γé╣3,150/sq.ft</t>
         </is>
       </c>
       <c r="K157" s="4" t="inlineStr">
@@ -18102,17 +18139,17 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>₹13.5 Lakhs</t>
+          <t>Γé╣13.5 Lakhs</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>₹13.5L - ₹25L</t>
+          <t>Γé╣13.5L - Γé╣25L</t>
         </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>₹3,050/sq.ft</t>
+          <t>Γé╣3,050/sq.ft</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -18184,17 +18221,17 @@
       </c>
       <c r="H159" s="4" t="inlineStr">
         <is>
-          <t>₹19 Lakhs</t>
+          <t>Γé╣19 Lakhs</t>
         </is>
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>₹19L - ₹33L</t>
+          <t>Γé╣19L - Γé╣33L</t>
         </is>
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
-          <t>₹3,450/sq.ft</t>
+          <t>Γé╣3,450/sq.ft</t>
         </is>
       </c>
       <c r="K159" s="4" t="inlineStr">
@@ -18266,17 +18303,17 @@
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>₹1.25 Cr</t>
+          <t>Γé╣1.25 Cr</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>₹1.25 Cr - ₹4.50 Cr</t>
+          <t>Γé╣1.25 Cr - Γé╣4.50 Cr</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>₹7,500/sq.ft</t>
+          <t>Γé╣7,500/sq.ft</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -18348,17 +18385,17 @@
       </c>
       <c r="H161" s="4" t="inlineStr">
         <is>
-          <t>₹1.45 Cr</t>
+          <t>Γé╣1.45 Cr</t>
         </is>
       </c>
       <c r="I161" s="4" t="inlineStr">
         <is>
-          <t>₹1.45 Cr - ₹3.80 Cr</t>
+          <t>Γé╣1.45 Cr - Γé╣3.80 Cr</t>
         </is>
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
-          <t>₹8,200/sq.ft</t>
+          <t>Γé╣8,200/sq.ft</t>
         </is>
       </c>
       <c r="K161" s="4" t="inlineStr">
@@ -18430,17 +18467,17 @@
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>₹95 Lakhs</t>
+          <t>Γé╣95 Lakhs</t>
         </is>
       </c>
       <c r="I162" s="2" t="inlineStr">
         <is>
-          <t>₹95L - ₹2.50 Cr</t>
+          <t>Γé╣95L - Γé╣2.50 Cr</t>
         </is>
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>₹7,800/sq.ft</t>
+          <t>Γé╣7,800/sq.ft</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -18512,17 +18549,17 @@
       </c>
       <c r="H163" s="4" t="inlineStr">
         <is>
-          <t>₹78 Lakhs</t>
+          <t>Γé╣78 Lakhs</t>
         </is>
       </c>
       <c r="I163" s="4" t="inlineStr">
         <is>
-          <t>₹78L - ₹1.75 Cr</t>
+          <t>Γé╣78L - Γé╣1.75 Cr</t>
         </is>
       </c>
       <c r="J163" s="4" t="inlineStr">
         <is>
-          <t>₹7,400/sq.ft</t>
+          <t>Γé╣7,400/sq.ft</t>
         </is>
       </c>
       <c r="K163" s="4" t="inlineStr">
@@ -18594,17 +18631,17 @@
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>₹65 Lakhs</t>
+          <t>Γé╣65 Lakhs</t>
         </is>
       </c>
       <c r="I164" s="2" t="inlineStr">
         <is>
-          <t>₹65L - ₹1.35 Cr</t>
+          <t>Γé╣65L - Γé╣1.35 Cr</t>
         </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>₹6,900/sq.ft</t>
+          <t>Γé╣6,900/sq.ft</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -18676,17 +18713,17 @@
       </c>
       <c r="H165" s="4" t="inlineStr">
         <is>
-          <t>₹18 Lakhs</t>
+          <t>Γé╣18 Lakhs</t>
         </is>
       </c>
       <c r="I165" s="4" t="inlineStr">
         <is>
-          <t>₹18L - ₹38L</t>
+          <t>Γé╣18L - Γé╣38L</t>
         </is>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
-          <t>₹3,900/sq.ft</t>
+          <t>Γé╣3,900/sq.ft</t>
         </is>
       </c>
       <c r="K165" s="4" t="inlineStr">
@@ -18758,17 +18795,17 @@
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>₹22 Lakhs</t>
+          <t>Γé╣22 Lakhs</t>
         </is>
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>₹22L - ₹42L</t>
+          <t>Γé╣22L - Γé╣42L</t>
         </is>
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>₹4,100/sq.ft</t>
+          <t>Γé╣4,100/sq.ft</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -18840,17 +18877,17 @@
       </c>
       <c r="H167" s="4" t="inlineStr">
         <is>
-          <t>₹16 Lakhs</t>
+          <t>Γé╣16 Lakhs</t>
         </is>
       </c>
       <c r="I167" s="4" t="inlineStr">
         <is>
-          <t>₹16L - ₹27L</t>
+          <t>Γé╣16L - Γé╣27L</t>
         </is>
       </c>
       <c r="J167" s="4" t="inlineStr">
         <is>
-          <t>₹3,700/sq.ft</t>
+          <t>Γé╣3,700/sq.ft</t>
         </is>
       </c>
       <c r="K167" s="4" t="inlineStr">
@@ -18922,17 +18959,17 @@
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>₹27 Lakhs</t>
+          <t>Γé╣27 Lakhs</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
         <is>
-          <t>₹27L - ₹54L</t>
+          <t>Γé╣27L - Γé╣54L</t>
         </is>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>₹4,300/sq.ft</t>
+          <t>Γé╣4,300/sq.ft</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -19004,17 +19041,17 @@
       </c>
       <c r="H169" s="4" t="inlineStr">
         <is>
-          <t>₹24 Lakhs</t>
+          <t>Γé╣24 Lakhs</t>
         </is>
       </c>
       <c r="I169" s="4" t="inlineStr">
         <is>
-          <t>₹24L - ₹44L</t>
+          <t>Γé╣24L - Γé╣44L</t>
         </is>
       </c>
       <c r="J169" s="4" t="inlineStr">
         <is>
-          <t>₹4,000/sq.ft</t>
+          <t>Γé╣4,000/sq.ft</t>
         </is>
       </c>
       <c r="K169" s="4" t="inlineStr">
@@ -19086,17 +19123,17 @@
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>₹19.5 Lakhs</t>
+          <t>Γé╣19.5 Lakhs</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>₹19.5L - ₹38L</t>
+          <t>Γé╣19.5L - Γé╣38L</t>
         </is>
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>₹3,950/sq.ft</t>
+          <t>Γé╣3,950/sq.ft</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -19168,17 +19205,17 @@
       </c>
       <c r="H171" s="4" t="inlineStr">
         <is>
-          <t>₹24 Lakhs</t>
+          <t>Γé╣24 Lakhs</t>
         </is>
       </c>
       <c r="I171" s="4" t="inlineStr">
         <is>
-          <t>₹24L - ₹46L</t>
+          <t>Γé╣24L - Γé╣46L</t>
         </is>
       </c>
       <c r="J171" s="4" t="inlineStr">
         <is>
-          <t>₹4,100/sq.ft</t>
+          <t>Γé╣4,100/sq.ft</t>
         </is>
       </c>
       <c r="K171" s="4" t="inlineStr">
@@ -19250,17 +19287,17 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>₹22.5 Lakhs</t>
+          <t>Γé╣22.5 Lakhs</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>₹22.5L - ₹41L</t>
+          <t>Γé╣22.5L - Γé╣41L</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>₹4,000/sq.ft</t>
+          <t>Γé╣4,000/sq.ft</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -19332,17 +19369,17 @@
       </c>
       <c r="H173" s="4" t="inlineStr">
         <is>
-          <t>₹29 Lakhs</t>
+          <t>Γé╣29 Lakhs</t>
         </is>
       </c>
       <c r="I173" s="4" t="inlineStr">
         <is>
-          <t>₹29L - ₹62L</t>
+          <t>Γé╣29L - Γé╣62L</t>
         </is>
       </c>
       <c r="J173" s="4" t="inlineStr">
         <is>
-          <t>₹4,450/sq.ft</t>
+          <t>Γé╣4,450/sq.ft</t>
         </is>
       </c>
       <c r="K173" s="4" t="inlineStr">
@@ -19414,17 +19451,17 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>₹26 Lakhs</t>
+          <t>Γé╣26 Lakhs</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>₹26L - ₹52L</t>
+          <t>Γé╣26L - Γé╣52L</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>₹4,300/sq.ft</t>
+          <t>Γé╣4,300/sq.ft</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
@@ -19496,17 +19533,17 @@
       </c>
       <c r="H175" s="4" t="inlineStr">
         <is>
-          <t>₹35 Lakhs</t>
+          <t>Γé╣35 Lakhs</t>
         </is>
       </c>
       <c r="I175" s="4" t="inlineStr">
         <is>
-          <t>₹35L - ₹78L</t>
+          <t>Γé╣35L - Γé╣78L</t>
         </is>
       </c>
       <c r="J175" s="4" t="inlineStr">
         <is>
-          <t>₹4,800/sq.ft</t>
+          <t>Γé╣4,800/sq.ft</t>
         </is>
       </c>
       <c r="K175" s="4" t="inlineStr">
@@ -19578,17 +19615,17 @@
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>₹33 Lakhs</t>
+          <t>Γé╣33 Lakhs</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
         <is>
-          <t>₹33L - ₹64L</t>
+          <t>Γé╣33L - Γé╣64L</t>
         </is>
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>₹4,650/sq.ft</t>
+          <t>Γé╣4,650/sq.ft</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr">
@@ -19660,17 +19697,17 @@
       </c>
       <c r="H177" s="4" t="inlineStr">
         <is>
-          <t>₹31 Lakhs</t>
+          <t>Γé╣31 Lakhs</t>
         </is>
       </c>
       <c r="I177" s="4" t="inlineStr">
         <is>
-          <t>₹31L - ₹58L</t>
+          <t>Γé╣31L - Γé╣58L</t>
         </is>
       </c>
       <c r="J177" s="4" t="inlineStr">
         <is>
-          <t>₹4,600/sq.ft</t>
+          <t>Γé╣4,600/sq.ft</t>
         </is>
       </c>
       <c r="K177" s="4" t="inlineStr">
@@ -19742,17 +19779,17 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>₹17 Lakhs</t>
+          <t>Γé╣17 Lakhs</t>
         </is>
       </c>
       <c r="I178" s="2" t="inlineStr">
         <is>
-          <t>₹17L - ₹32L</t>
+          <t>Γé╣17L - Γé╣32L</t>
         </is>
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>₹4,200/sq.ft</t>
+          <t>Γé╣4,200/sq.ft</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
@@ -19824,17 +19861,17 @@
       </c>
       <c r="H179" s="4" t="inlineStr">
         <is>
-          <t>₹23 Lakhs</t>
+          <t>Γé╣23 Lakhs</t>
         </is>
       </c>
       <c r="I179" s="4" t="inlineStr">
         <is>
-          <t>₹23L - ₹44L</t>
+          <t>Γé╣23L - Γé╣44L</t>
         </is>
       </c>
       <c r="J179" s="4" t="inlineStr">
         <is>
-          <t>₹3,900/sq.ft</t>
+          <t>Γé╣3,900/sq.ft</t>
         </is>
       </c>
       <c r="K179" s="4" t="inlineStr">
@@ -19906,17 +19943,17 @@
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>₹27 Lakhs</t>
+          <t>Γé╣27 Lakhs</t>
         </is>
       </c>
       <c r="I180" s="2" t="inlineStr">
         <is>
-          <t>₹27L - ₹51L</t>
+          <t>Γé╣27L - Γé╣51L</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>₹4,250/sq.ft</t>
+          <t>Γé╣4,250/sq.ft</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr">
@@ -19988,17 +20025,17 @@
       </c>
       <c r="H181" s="4" t="inlineStr">
         <is>
-          <t>₹21 Lakhs</t>
+          <t>Γé╣21 Lakhs</t>
         </is>
       </c>
       <c r="I181" s="4" t="inlineStr">
         <is>
-          <t>₹21L - ₹40L</t>
+          <t>Γé╣21L - Γé╣40L</t>
         </is>
       </c>
       <c r="J181" s="4" t="inlineStr">
         <is>
-          <t>₹3,850/sq.ft</t>
+          <t>Γé╣3,850/sq.ft</t>
         </is>
       </c>
       <c r="K181" s="4" t="inlineStr">
@@ -20070,17 +20107,17 @@
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>₹25 Lakhs</t>
+          <t>Γé╣25 Lakhs</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>₹25L - ₹48L</t>
+          <t>Γé╣25L - Γé╣48L</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>₹4,100/sq.ft</t>
+          <t>Γé╣4,100/sq.ft</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr">
@@ -20152,17 +20189,17 @@
       </c>
       <c r="H183" s="4" t="inlineStr">
         <is>
-          <t>₹22 Lakhs</t>
+          <t>Γé╣22 Lakhs</t>
         </is>
       </c>
       <c r="I183" s="4" t="inlineStr">
         <is>
-          <t>₹22L - ₹42L</t>
+          <t>Γé╣22L - Γé╣42L</t>
         </is>
       </c>
       <c r="J183" s="4" t="inlineStr">
         <is>
-          <t>₹3,850/sq.ft</t>
+          <t>Γé╣3,850/sq.ft</t>
         </is>
       </c>
       <c r="K183" s="4" t="inlineStr">
@@ -20234,17 +20271,17 @@
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>₹15 Lakhs</t>
+          <t>Γé╣15 Lakhs</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>₹15L - ₹34L</t>
+          <t>Γé╣15L - Γé╣34L</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>₹3,550/sq.ft</t>
+          <t>Γé╣3,550/sq.ft</t>
         </is>
       </c>
       <c r="K184" s="2" t="inlineStr">
@@ -20316,17 +20353,17 @@
       </c>
       <c r="H185" s="4" t="inlineStr">
         <is>
-          <t>₹20 Lakhs</t>
+          <t>Γé╣20 Lakhs</t>
         </is>
       </c>
       <c r="I185" s="4" t="inlineStr">
         <is>
-          <t>₹20L - ₹39L</t>
+          <t>Γé╣20L - Γé╣39L</t>
         </is>
       </c>
       <c r="J185" s="4" t="inlineStr">
         <is>
-          <t>₹3,750/sq.ft</t>
+          <t>Γé╣3,750/sq.ft</t>
         </is>
       </c>
       <c r="K185" s="4" t="inlineStr">
@@ -20398,17 +20435,17 @@
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>₹18.5 Lakhs</t>
+          <t>Γé╣18.5 Lakhs</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>₹18.5L - ₹45L</t>
+          <t>Γé╣18.5L - Γé╣45L</t>
         </is>
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>₹3,400/sq.ft</t>
+          <t>Γé╣3,400/sq.ft</t>
         </is>
       </c>
       <c r="K186" s="2" t="inlineStr">
@@ -20480,17 +20517,17 @@
       </c>
       <c r="H187" s="4" t="inlineStr">
         <is>
-          <t>₹17 Lakhs</t>
+          <t>Γé╣17 Lakhs</t>
         </is>
       </c>
       <c r="I187" s="4" t="inlineStr">
         <is>
-          <t>₹17L - ₹35L</t>
+          <t>Γé╣17L - Γé╣35L</t>
         </is>
       </c>
       <c r="J187" s="4" t="inlineStr">
         <is>
-          <t>₹3,650/sq.ft</t>
+          <t>Γé╣3,650/sq.ft</t>
         </is>
       </c>
       <c r="K187" s="4" t="inlineStr">
@@ -20562,17 +20599,17 @@
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>₹32 Lakhs</t>
+          <t>Γé╣32 Lakhs</t>
         </is>
       </c>
       <c r="I188" s="2" t="inlineStr">
         <is>
-          <t>₹32L - ₹70L</t>
+          <t>Γé╣32L - Γé╣70L</t>
         </is>
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>₹5,200/sq.ft</t>
+          <t>Γé╣5,200/sq.ft</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr">
@@ -20644,17 +20681,17 @@
       </c>
       <c r="H189" s="4" t="inlineStr">
         <is>
-          <t>₹36 Lakhs</t>
+          <t>Γé╣36 Lakhs</t>
         </is>
       </c>
       <c r="I189" s="4" t="inlineStr">
         <is>
-          <t>₹36L - ₹82L</t>
+          <t>Γé╣36L - Γé╣82L</t>
         </is>
       </c>
       <c r="J189" s="4" t="inlineStr">
         <is>
-          <t>₹5,400/sq.ft</t>
+          <t>Γé╣5,400/sq.ft</t>
         </is>
       </c>
       <c r="K189" s="4" t="inlineStr">
@@ -20726,17 +20763,17 @@
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>₹28 Lakhs</t>
+          <t>Γé╣28 Lakhs</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>₹28L - ₹65L</t>
+          <t>Γé╣28L - Γé╣65L</t>
         </is>
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>₹5,100/sq.ft</t>
+          <t>Γé╣5,100/sq.ft</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr">
@@ -20808,17 +20845,17 @@
       </c>
       <c r="H191" s="4" t="inlineStr">
         <is>
-          <t>₹30 Lakhs</t>
+          <t>Γé╣30 Lakhs</t>
         </is>
       </c>
       <c r="I191" s="4" t="inlineStr">
         <is>
-          <t>₹30L - ₹58L</t>
+          <t>Γé╣30L - Γé╣58L</t>
         </is>
       </c>
       <c r="J191" s="4" t="inlineStr">
         <is>
-          <t>₹4,900/sq.ft</t>
+          <t>Γé╣4,900/sq.ft</t>
         </is>
       </c>
       <c r="K191" s="4" t="inlineStr">
@@ -20890,17 +20927,17 @@
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>₹18 Lakhs</t>
+          <t>Γé╣18 Lakhs</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>₹18L - ₹38L</t>
+          <t>Γé╣18L - Γé╣38L</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>₹4,300/sq.ft</t>
+          <t>Γé╣4,300/sq.ft</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr">
@@ -20972,17 +21009,17 @@
       </c>
       <c r="H193" s="4" t="inlineStr">
         <is>
-          <t>₹38 Lakhs</t>
+          <t>Γé╣38 Lakhs</t>
         </is>
       </c>
       <c r="I193" s="4" t="inlineStr">
         <is>
-          <t>₹38L - ₹68L</t>
+          <t>Γé╣38L - Γé╣68L</t>
         </is>
       </c>
       <c r="J193" s="4" t="inlineStr">
         <is>
-          <t>₹5,600/sq.ft</t>
+          <t>Γé╣5,600/sq.ft</t>
         </is>
       </c>
       <c r="K193" s="4" t="inlineStr">
@@ -21054,17 +21091,17 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>₹65 Lakhs</t>
+          <t>Γé╣65 Lakhs</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>₹65L - ₹1.10 Cr</t>
+          <t>Γé╣65L - Γé╣1.10 Cr</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>₹6,400/sq.ft</t>
+          <t>Γé╣6,400/sq.ft</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr">
@@ -21136,17 +21173,17 @@
       </c>
       <c r="H195" s="4" t="inlineStr">
         <is>
-          <t>₹28 Lakhs</t>
+          <t>Γé╣28 Lakhs</t>
         </is>
       </c>
       <c r="I195" s="4" t="inlineStr">
         <is>
-          <t>₹28L - ₹54L</t>
+          <t>Γé╣28L - Γé╣54L</t>
         </is>
       </c>
       <c r="J195" s="4" t="inlineStr">
         <is>
-          <t>₹4,500/sq.ft</t>
+          <t>Γé╣4,500/sq.ft</t>
         </is>
       </c>
       <c r="K195" s="4" t="inlineStr">
@@ -21218,17 +21255,17 @@
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>₹22 Lakhs</t>
+          <t>Γé╣22 Lakhs</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>₹22L - ₹48L</t>
+          <t>Γé╣22L - Γé╣48L</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>₹4,600/sq.ft</t>
+          <t>Γé╣4,600/sq.ft</t>
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr">
@@ -21300,17 +21337,17 @@
       </c>
       <c r="H197" s="4" t="inlineStr">
         <is>
-          <t>₹16 Lakhs</t>
+          <t>Γé╣16 Lakhs</t>
         </is>
       </c>
       <c r="I197" s="4" t="inlineStr">
         <is>
-          <t>₹16L - ₹35L</t>
+          <t>Γé╣16L - Γé╣35L</t>
         </is>
       </c>
       <c r="J197" s="4" t="inlineStr">
         <is>
-          <t>₹3,400/sq.ft</t>
+          <t>Γé╣3,400/sq.ft</t>
         </is>
       </c>
       <c r="K197" s="4" t="inlineStr">
@@ -21382,17 +21419,17 @@
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>₹45 Lakhs</t>
+          <t>Γé╣45 Lakhs</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>₹45L - ₹98L</t>
+          <t>Γé╣45L - Γé╣98L</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>₹6,100/sq.ft</t>
+          <t>Γé╣6,100/sq.ft</t>
         </is>
       </c>
       <c r="K198" s="2" t="inlineStr">
@@ -21464,17 +21501,17 @@
       </c>
       <c r="H199" s="4" t="inlineStr">
         <is>
-          <t>₹55 Lakhs</t>
+          <t>Γé╣55 Lakhs</t>
         </is>
       </c>
       <c r="I199" s="4" t="inlineStr">
         <is>
-          <t>₹55L - ₹1.15 Cr</t>
+          <t>Γé╣55L - Γé╣1.15 Cr</t>
         </is>
       </c>
       <c r="J199" s="4" t="inlineStr">
         <is>
-          <t>₹7,200/sq.ft</t>
+          <t>Γé╣7,200/sq.ft</t>
         </is>
       </c>
       <c r="K199" s="4" t="inlineStr">
@@ -21546,17 +21583,17 @@
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>₹1.45 Cr</t>
+          <t>Γé╣1.45 Cr</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>₹1.45 Cr - ₹4.50 Cr</t>
+          <t>Γé╣1.45 Cr - Γé╣4.50 Cr</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>₹15,500/sq.ft</t>
+          <t>Γé╣15,500/sq.ft</t>
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr">
@@ -21628,17 +21665,17 @@
       </c>
       <c r="H201" s="4" t="inlineStr">
         <is>
-          <t>₹75 Lakhs</t>
+          <t>Γé╣75 Lakhs</t>
         </is>
       </c>
       <c r="I201" s="4" t="inlineStr">
         <is>
-          <t>₹75L - ₹1.85 Cr</t>
+          <t>Γé╣75L - Γé╣1.85 Cr</t>
         </is>
       </c>
       <c r="J201" s="4" t="inlineStr">
         <is>
-          <t>₹12,800/sq.ft</t>
+          <t>Γé╣12,800/sq.ft</t>
         </is>
       </c>
       <c r="K201" s="4" t="inlineStr">
@@ -21710,17 +21747,17 @@
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>₹62 Lakhs</t>
+          <t>Γé╣62 Lakhs</t>
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>₹62L - ₹1.60 Cr</t>
+          <t>Γé╣62L - Γé╣1.60 Cr</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>₹10,500/sq.ft</t>
+          <t>Γé╣10,500/sq.ft</t>
         </is>
       </c>
       <c r="K202" s="2" t="inlineStr">
@@ -21792,17 +21829,17 @@
       </c>
       <c r="H203" s="4" t="inlineStr">
         <is>
-          <t>₹68 Lakhs</t>
+          <t>Γé╣68 Lakhs</t>
         </is>
       </c>
       <c r="I203" s="4" t="inlineStr">
         <is>
-          <t>₹68L - ₹1.25 Cr</t>
+          <t>Γé╣68L - Γé╣1.25 Cr</t>
         </is>
       </c>
       <c r="J203" s="4" t="inlineStr">
         <is>
-          <t>₹13,200/sq.ft</t>
+          <t>Γé╣13,200/sq.ft</t>
         </is>
       </c>
       <c r="K203" s="4" t="inlineStr">
@@ -21874,17 +21911,17 @@
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>₹58 Lakhs</t>
+          <t>Γé╣58 Lakhs</t>
         </is>
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>₹58L - ₹1.75 Cr</t>
+          <t>Γé╣58L - Γé╣1.75 Cr</t>
         </is>
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>₹10,200/sq.ft</t>
+          <t>Γé╣10,200/sq.ft</t>
         </is>
       </c>
       <c r="K204" s="2" t="inlineStr">
@@ -21956,17 +21993,17 @@
       </c>
       <c r="H205" s="4" t="inlineStr">
         <is>
-          <t>₹28 Lakhs</t>
+          <t>Γé╣28 Lakhs</t>
         </is>
       </c>
       <c r="I205" s="4" t="inlineStr">
         <is>
-          <t>₹28L - ₹52L</t>
+          <t>Γé╣28L - Γé╣52L</t>
         </is>
       </c>
       <c r="J205" s="4" t="inlineStr">
         <is>
-          <t>₹5,400/sq.ft</t>
+          <t>Γé╣5,400/sq.ft</t>
         </is>
       </c>
       <c r="K205" s="4" t="inlineStr">
@@ -22038,17 +22075,17 @@
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>₹82 Lakhs</t>
+          <t>Γé╣82 Lakhs</t>
         </is>
       </c>
       <c r="I206" s="2" t="inlineStr">
         <is>
-          <t>₹82L - ₹2.10 Cr</t>
+          <t>Γé╣82L - Γé╣2.10 Cr</t>
         </is>
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>₹8,500/sq.ft</t>
+          <t>Γé╣8,500/sq.ft</t>
         </is>
       </c>
       <c r="K206" s="2" t="inlineStr">
@@ -22120,17 +22157,17 @@
       </c>
       <c r="H207" s="4" t="inlineStr">
         <is>
-          <t>₹44 Lakhs</t>
+          <t>Γé╣44 Lakhs</t>
         </is>
       </c>
       <c r="I207" s="4" t="inlineStr">
         <is>
-          <t>₹44L - ₹85L</t>
+          <t>Γé╣44L - Γé╣85L</t>
         </is>
       </c>
       <c r="J207" s="4" t="inlineStr">
         <is>
-          <t>₹7,800/sq.ft</t>
+          <t>Γé╣7,800/sq.ft</t>
         </is>
       </c>
       <c r="K207" s="4" t="inlineStr">
@@ -22202,17 +22239,17 @@
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>₹18 Lakhs</t>
+          <t>Γé╣18 Lakhs</t>
         </is>
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>₹18L - ₹36L</t>
+          <t>Γé╣18L - Γé╣36L</t>
         </is>
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>₹3,900/sq.ft</t>
+          <t>Γé╣3,900/sq.ft</t>
         </is>
       </c>
       <c r="K208" s="2" t="inlineStr">
@@ -22284,17 +22321,17 @@
       </c>
       <c r="H209" s="4" t="inlineStr">
         <is>
-          <t>₹25 Lakhs</t>
+          <t>Γé╣25 Lakhs</t>
         </is>
       </c>
       <c r="I209" s="4" t="inlineStr">
         <is>
-          <t>₹25L - ₹47L</t>
+          <t>Γé╣25L - Γé╣47L</t>
         </is>
       </c>
       <c r="J209" s="4" t="inlineStr">
         <is>
-          <t>₹4,150/sq.ft</t>
+          <t>Γé╣4,150/sq.ft</t>
         </is>
       </c>
       <c r="K209" s="4" t="inlineStr">
@@ -22366,17 +22403,17 @@
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>₹32 Lakhs</t>
+          <t>Γé╣32 Lakhs</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>₹32L - ₹59L</t>
+          <t>Γé╣32L - Γé╣59L</t>
         </is>
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>₹4,650/sq.ft</t>
+          <t>Γé╣4,650/sq.ft</t>
         </is>
       </c>
       <c r="K210" s="2" t="inlineStr">
@@ -22448,17 +22485,17 @@
       </c>
       <c r="H211" s="4" t="inlineStr">
         <is>
-          <t>₹29 Lakhs</t>
+          <t>Γé╣29 Lakhs</t>
         </is>
       </c>
       <c r="I211" s="4" t="inlineStr">
         <is>
-          <t>₹29L - ₹55L</t>
+          <t>Γé╣29L - Γé╣55L</t>
         </is>
       </c>
       <c r="J211" s="4" t="inlineStr">
         <is>
-          <t>₹4,400/sq.ft</t>
+          <t>Γé╣4,400/sq.ft</t>
         </is>
       </c>
       <c r="K211" s="4" t="inlineStr">
@@ -22530,17 +22567,17 @@
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>₹22 Lakhs</t>
+          <t>Γé╣22 Lakhs</t>
         </is>
       </c>
       <c r="I212" s="2" t="inlineStr">
         <is>
-          <t>₹22L - ₹49L</t>
+          <t>Γé╣22L - Γé╣49L</t>
         </is>
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>₹4,500/sq.ft</t>
+          <t>Γé╣4,500/sq.ft</t>
         </is>
       </c>
       <c r="K212" s="2" t="inlineStr">
@@ -22612,17 +22649,17 @@
       </c>
       <c r="H213" s="4" t="inlineStr">
         <is>
-          <t>₹26 Lakhs</t>
+          <t>Γé╣26 Lakhs</t>
         </is>
       </c>
       <c r="I213" s="4" t="inlineStr">
         <is>
-          <t>₹26L - ₹51L</t>
+          <t>Γé╣26L - Γé╣51L</t>
         </is>
       </c>
       <c r="J213" s="4" t="inlineStr">
         <is>
-          <t>₹4,100/sq.ft</t>
+          <t>Γé╣4,100/sq.ft</t>
         </is>
       </c>
       <c r="K213" s="4" t="inlineStr">
@@ -22694,17 +22731,17 @@
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>₹19 Lakhs</t>
+          <t>Γé╣19 Lakhs</t>
         </is>
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>₹19L - ₹39L</t>
+          <t>Γé╣19L - Γé╣39L</t>
         </is>
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>₹3,800/sq.ft</t>
+          <t>Γé╣3,800/sq.ft</t>
         </is>
       </c>
       <c r="K214" s="2" t="inlineStr">
@@ -22776,17 +22813,17 @@
       </c>
       <c r="H215" s="4" t="inlineStr">
         <is>
-          <t>₹17.5 Lakhs</t>
+          <t>Γé╣17.5 Lakhs</t>
         </is>
       </c>
       <c r="I215" s="4" t="inlineStr">
         <is>
-          <t>₹17.5L - ₹34L</t>
+          <t>Γé╣17.5L - Γé╣34L</t>
         </is>
       </c>
       <c r="J215" s="4" t="inlineStr">
         <is>
-          <t>₹3,500/sq.ft</t>
+          <t>Γé╣3,500/sq.ft</t>
         </is>
       </c>
       <c r="K215" s="4" t="inlineStr">
@@ -22858,17 +22895,17 @@
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>₹35 Lakhs</t>
+          <t>Γé╣35 Lakhs</t>
         </is>
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>₹35L - ₹75L</t>
+          <t>Γé╣35L - Γé╣75L</t>
         </is>
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>₹5,300/sq.ft</t>
+          <t>Γé╣5,300/sq.ft</t>
         </is>
       </c>
       <c r="K216" s="2" t="inlineStr">
@@ -22940,17 +22977,17 @@
       </c>
       <c r="H217" s="4" t="inlineStr">
         <is>
-          <t>₹26 Lakhs</t>
+          <t>Γé╣26 Lakhs</t>
         </is>
       </c>
       <c r="I217" s="4" t="inlineStr">
         <is>
-          <t>₹26L - ₹52L</t>
+          <t>Γé╣26L - Γé╣52L</t>
         </is>
       </c>
       <c r="J217" s="4" t="inlineStr">
         <is>
-          <t>₹4,950/sq.ft</t>
+          <t>Γé╣4,950/sq.ft</t>
         </is>
       </c>
       <c r="K217" s="4" t="inlineStr">
@@ -23022,17 +23059,17 @@
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>₹29 Lakhs</t>
+          <t>Γé╣29 Lakhs</t>
         </is>
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>₹29L - ₹58L</t>
+          <t>Γé╣29L - Γé╣58L</t>
         </is>
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
-          <t>₹5,100/sq.ft</t>
+          <t>Γé╣5,100/sq.ft</t>
         </is>
       </c>
       <c r="K218" s="2" t="inlineStr">
@@ -23104,17 +23141,17 @@
       </c>
       <c r="H219" s="4" t="inlineStr">
         <is>
-          <t>₹17 Lakhs</t>
+          <t>Γé╣17 Lakhs</t>
         </is>
       </c>
       <c r="I219" s="4" t="inlineStr">
         <is>
-          <t>₹17L - ₹37L</t>
+          <t>Γé╣17L - Γé╣37L</t>
         </is>
       </c>
       <c r="J219" s="4" t="inlineStr">
         <is>
-          <t>₹4,200/sq.ft</t>
+          <t>Γé╣4,200/sq.ft</t>
         </is>
       </c>
       <c r="K219" s="4" t="inlineStr">
@@ -23186,17 +23223,17 @@
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>₹58 Lakhs</t>
+          <t>Γé╣58 Lakhs</t>
         </is>
       </c>
       <c r="I220" s="2" t="inlineStr">
         <is>
-          <t>₹58L - ₹95L</t>
+          <t>Γé╣58L - Γé╣95L</t>
         </is>
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>₹6,200/sq.ft</t>
+          <t>Γé╣6,200/sq.ft</t>
         </is>
       </c>
       <c r="K220" s="2" t="inlineStr">
@@ -23268,17 +23305,17 @@
       </c>
       <c r="H221" s="4" t="inlineStr">
         <is>
-          <t>₹26 Lakhs</t>
+          <t>Γé╣26 Lakhs</t>
         </is>
       </c>
       <c r="I221" s="4" t="inlineStr">
         <is>
-          <t>₹26L - ₹49L</t>
+          <t>Γé╣26L - Γé╣49L</t>
         </is>
       </c>
       <c r="J221" s="4" t="inlineStr">
         <is>
-          <t>₹4,400/sq.ft</t>
+          <t>Γé╣4,400/sq.ft</t>
         </is>
       </c>
       <c r="K221" s="4" t="inlineStr">
@@ -23350,17 +23387,17 @@
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>₹15 Lakhs</t>
+          <t>Γé╣15 Lakhs</t>
         </is>
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>₹15L - ₹32L</t>
+          <t>Γé╣15L - Γé╣32L</t>
         </is>
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>₹3,350/sq.ft</t>
+          <t>Γé╣3,350/sq.ft</t>
         </is>
       </c>
       <c r="K222" s="2" t="inlineStr">
@@ -23432,17 +23469,17 @@
       </c>
       <c r="H223" s="4" t="inlineStr">
         <is>
-          <t>₹42 Lakhs</t>
+          <t>Γé╣42 Lakhs</t>
         </is>
       </c>
       <c r="I223" s="4" t="inlineStr">
         <is>
-          <t>₹42L - ₹88L</t>
+          <t>Γé╣42L - Γé╣88L</t>
         </is>
       </c>
       <c r="J223" s="4" t="inlineStr">
         <is>
-          <t>₹5,800/sq.ft</t>
+          <t>Γé╣5,800/sq.ft</t>
         </is>
       </c>
       <c r="K223" s="4" t="inlineStr">
@@ -23514,17 +23551,17 @@
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>₹29 Lakhs</t>
+          <t>Γé╣29 Lakhs</t>
         </is>
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>₹29L - ₹54L</t>
+          <t>Γé╣29L - Γé╣54L</t>
         </is>
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>₹4,700/sq.ft</t>
+          <t>Γé╣4,700/sq.ft</t>
         </is>
       </c>
       <c r="K224" s="2" t="inlineStr">
@@ -23596,17 +23633,17 @@
       </c>
       <c r="H225" s="4" t="inlineStr">
         <is>
-          <t>₹52 Lakhs</t>
+          <t>Γé╣52 Lakhs</t>
         </is>
       </c>
       <c r="I225" s="4" t="inlineStr">
         <is>
-          <t>₹52L - ₹95L</t>
+          <t>Γé╣52L - Γé╣95L</t>
         </is>
       </c>
       <c r="J225" s="4" t="inlineStr">
         <is>
-          <t>₹6,900/sq.ft</t>
+          <t>Γé╣6,900/sq.ft</t>
         </is>
       </c>
       <c r="K225" s="4" t="inlineStr">
@@ -23678,17 +23715,17 @@
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>₹56 Lakhs</t>
+          <t>Γé╣56 Lakhs</t>
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>₹56L - ₹92L</t>
+          <t>Γé╣56L - Γé╣92L</t>
         </is>
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>₹11,000/sq.ft</t>
+          <t>Γé╣11,000/sq.ft</t>
         </is>
       </c>
       <c r="K226" s="2" t="inlineStr">
@@ -23760,17 +23797,17 @@
       </c>
       <c r="H227" s="4" t="inlineStr">
         <is>
-          <t>₹1.15 Cr</t>
+          <t>Γé╣1.15 Cr</t>
         </is>
       </c>
       <c r="I227" s="4" t="inlineStr">
         <is>
-          <t>₹1.15 Cr - ₹2.80 Cr</t>
+          <t>Γé╣1.15 Cr - Γé╣2.80 Cr</t>
         </is>
       </c>
       <c r="J227" s="4" t="inlineStr">
         <is>
-          <t>₹14,500/sq.ft</t>
+          <t>Γé╣14,500/sq.ft</t>
         </is>
       </c>
       <c r="K227" s="4" t="inlineStr">
@@ -23842,17 +23879,17 @@
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>₹34 Lakhs</t>
+          <t>Γé╣34 Lakhs</t>
         </is>
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>₹34L - ₹62L</t>
+          <t>Γé╣34L - Γé╣62L</t>
         </is>
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
-          <t>₹5,800/sq.ft</t>
+          <t>Γé╣5,800/sq.ft</t>
         </is>
       </c>
       <c r="K228" s="2" t="inlineStr">
@@ -23924,17 +23961,17 @@
       </c>
       <c r="H229" s="4" t="inlineStr">
         <is>
-          <t>₹48 Lakhs</t>
+          <t>Γé╣48 Lakhs</t>
         </is>
       </c>
       <c r="I229" s="4" t="inlineStr">
         <is>
-          <t>₹48L - ₹90L</t>
+          <t>Γé╣48L - Γé╣90L</t>
         </is>
       </c>
       <c r="J229" s="4" t="inlineStr">
         <is>
-          <t>₹8,100/sq.ft</t>
+          <t>Γé╣8,100/sq.ft</t>
         </is>
       </c>
       <c r="K229" s="4" t="inlineStr">
@@ -24006,17 +24043,17 @@
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>₹28 Lakhs</t>
+          <t>Γé╣28 Lakhs</t>
         </is>
       </c>
       <c r="I230" s="2" t="inlineStr">
         <is>
-          <t>₹28L - ₹49L</t>
+          <t>Γé╣28L - Γé╣49L</t>
         </is>
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
-          <t>₹4,800/sq.ft</t>
+          <t>Γé╣4,800/sq.ft</t>
         </is>
       </c>
       <c r="K230" s="2" t="inlineStr">
@@ -24088,17 +24125,17 @@
       </c>
       <c r="H231" s="4" t="inlineStr">
         <is>
-          <t>₹34 Lakhs</t>
+          <t>Γé╣34 Lakhs</t>
         </is>
       </c>
       <c r="I231" s="4" t="inlineStr">
         <is>
-          <t>₹34L - ₹64L</t>
+          <t>Γé╣34L - Γé╣64L</t>
         </is>
       </c>
       <c r="J231" s="4" t="inlineStr">
         <is>
-          <t>₹5,200/sq.ft</t>
+          <t>Γé╣5,200/sq.ft</t>
         </is>
       </c>
       <c r="K231" s="4" t="inlineStr">
@@ -24170,17 +24207,17 @@
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>₹59 Lakhs</t>
+          <t>Γé╣59 Lakhs</t>
         </is>
       </c>
       <c r="I232" s="2" t="inlineStr">
         <is>
-          <t>₹59L - ₹1.10 Cr</t>
+          <t>Γé╣59L - Γé╣1.10 Cr</t>
         </is>
       </c>
       <c r="J232" s="2" t="inlineStr">
         <is>
-          <t>₹6,100/sq.ft</t>
+          <t>Γé╣6,100/sq.ft</t>
         </is>
       </c>
       <c r="K232" s="2" t="inlineStr">
@@ -24252,17 +24289,17 @@
       </c>
       <c r="H233" s="4" t="inlineStr">
         <is>
-          <t>₹48 Lakhs</t>
+          <t>Γé╣48 Lakhs</t>
         </is>
       </c>
       <c r="I233" s="4" t="inlineStr">
         <is>
-          <t>₹48L - ₹95L</t>
+          <t>Γé╣48L - Γé╣95L</t>
         </is>
       </c>
       <c r="J233" s="4" t="inlineStr">
         <is>
-          <t>₹6,400/sq.ft</t>
+          <t>Γé╣6,400/sq.ft</t>
         </is>
       </c>
       <c r="K233" s="4" t="inlineStr">
@@ -24334,17 +24371,17 @@
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>₹38 Lakhs</t>
+          <t>Γé╣38 Lakhs</t>
         </is>
       </c>
       <c r="I234" s="2" t="inlineStr">
         <is>
-          <t>₹38L - ₹85L</t>
+          <t>Γé╣38L - Γé╣85L</t>
         </is>
       </c>
       <c r="J234" s="2" t="inlineStr">
         <is>
-          <t>₹4,900/sq.ft</t>
+          <t>Γé╣4,900/sq.ft</t>
         </is>
       </c>
       <c r="K234" s="2" t="inlineStr">
@@ -24416,17 +24453,17 @@
       </c>
       <c r="H235" s="4" t="inlineStr">
         <is>
-          <t>₹14.5 Lakhs</t>
+          <t>Γé╣14.5 Lakhs</t>
         </is>
       </c>
       <c r="I235" s="4" t="inlineStr">
         <is>
-          <t>₹14.5L - ₹31L</t>
+          <t>Γé╣14.5L - Γé╣31L</t>
         </is>
       </c>
       <c r="J235" s="4" t="inlineStr">
         <is>
-          <t>₹3,300/sq.ft</t>
+          <t>Γé╣3,300/sq.ft</t>
         </is>
       </c>
       <c r="K235" s="4" t="inlineStr">
@@ -24498,17 +24535,17 @@
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>₹12.5 Lakhs</t>
+          <t>Γé╣12.5 Lakhs</t>
         </is>
       </c>
       <c r="I236" s="2" t="inlineStr">
         <is>
-          <t>₹12.5L - ₹27L</t>
+          <t>Γé╣12.5L - Γé╣27L</t>
         </is>
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
-          <t>₹2,950/sq.ft</t>
+          <t>Γé╣2,950/sq.ft</t>
         </is>
       </c>
       <c r="K236" s="2" t="inlineStr">
@@ -24580,17 +24617,17 @@
       </c>
       <c r="H237" s="4" t="inlineStr">
         <is>
-          <t>₹19 Lakhs</t>
+          <t>Γé╣19 Lakhs</t>
         </is>
       </c>
       <c r="I237" s="4" t="inlineStr">
         <is>
-          <t>₹19L - ₹38L</t>
+          <t>Γé╣19L - Γé╣38L</t>
         </is>
       </c>
       <c r="J237" s="4" t="inlineStr">
         <is>
-          <t>₹3,400/sq.ft</t>
+          <t>Γé╣3,400/sq.ft</t>
         </is>
       </c>
       <c r="K237" s="4" t="inlineStr">
@@ -24662,17 +24699,17 @@
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>₹32 Lakhs</t>
+          <t>Γé╣32 Lakhs</t>
         </is>
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
-          <t>₹32L - ₹75L</t>
+          <t>Γé╣32L - Γé╣75L</t>
         </is>
       </c>
       <c r="J238" s="2" t="inlineStr">
         <is>
-          <t>₹4,600/sq.ft</t>
+          <t>Γé╣4,600/sq.ft</t>
         </is>
       </c>
       <c r="K238" s="2" t="inlineStr">
@@ -24744,17 +24781,17 @@
       </c>
       <c r="H239" s="4" t="inlineStr">
         <is>
-          <t>₹1.95 Cr</t>
+          <t>Γé╣1.95 Cr</t>
         </is>
       </c>
       <c r="I239" s="4" t="inlineStr">
         <is>
-          <t>₹1.95 Cr - ₹4.80 Cr</t>
+          <t>Γé╣1.95 Cr - Γé╣4.80 Cr</t>
         </is>
       </c>
       <c r="J239" s="4" t="inlineStr">
         <is>
-          <t>₹28,500/sq.ft</t>
+          <t>Γé╣28,500/sq.ft</t>
         </is>
       </c>
       <c r="K239" s="4" t="inlineStr">

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T22:54:03.321597</t>
+          <t>2026-10-28T22:59:17.907307</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28T22:54:03.321608</t>
+          <t>2026-10-28T22:59:17.907312</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T22:54:03.321618</t>
+          <t>2026-10-28T22:59:17.907317</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28T22:54:03.321587</t>
+          <t>2026-10-28T22:59:17.907302</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T22:54:03.321576</t>
+          <t>2026-10-28T22:59:17.907297</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28T22:54:03.321563</t>
+          <t>2026-10-28T22:59:17.907291</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1281,7 +1281,7 @@
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T22:54:03.321523</t>
+          <t>2026-10-28T22:59:17.907274</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       <c r="I11" s="4" t="inlineStr"/>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28T22:54:03.319933</t>
+          <t>2026-10-28T22:59:17.906628</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28T22:54:03.345638</t>
+          <t>2026-10-28T22:59:17.913900</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T22:54:03.348489</t>
+          <t>2026-10-28T22:59:17.914950</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28T22:54:03.348541</t>
+          <t>2026-10-28T22:59:17.914990</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T22:54:03.348557</t>
+          <t>2026-10-28T22:59:17.914998</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28T22:54:03.348571</t>
+          <t>2026-10-28T22:59:17.915004</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T22:54:03.348583</t>
+          <t>2026-10-28T22:59:17.915009</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28T22:54:03.348601</t>
+          <t>2026-10-28T22:59:17.915018</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T22:54:03.348613</t>
+          <t>2026-10-28T22:59:17.915023</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1842,7 +1842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5191,6 +5191,80 @@
       <c r="G92" s="2" t="inlineStr">
         <is>
           <t>2026-10-28T21:02:58.038864</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="22" customHeight="1">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1793208556411</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 28 Oct]</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28T22:59:17.922179</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="22" customHeight="1">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1793208469670</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 28 Oct]</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-28T22:59:17.923381</t>
         </is>
       </c>
     </row>

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -776,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T22:59:17.907307</t>
+          <t>2026-10-29T01:23:10.360759</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28T22:59:17.907312</t>
+          <t>2026-10-29T01:23:10.360767</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T22:59:17.907317</t>
+          <t>2026-10-29T01:23:10.360774</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28T22:59:17.907302</t>
+          <t>2026-10-29T01:23:10.360751</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T22:59:17.907297</t>
+          <t>2026-10-29T01:23:10.360743</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28T22:59:17.907291</t>
+          <t>2026-10-29T01:23:10.360734</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1281,7 +1281,7 @@
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T22:59:17.907274</t>
+          <t>2026-10-29T01:23:10.360724</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       <c r="I11" s="4" t="inlineStr"/>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28T22:59:17.906628</t>
+          <t>2026-10-29T01:23:10.360687</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -1385,6 +1385,55 @@
       <c r="K12" s="2" t="inlineStr">
         <is>
           <t>2026-10-26T21:05:18.434760</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>+916260347690</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>VIKASH</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>New Inquiry</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Rent Agreement (₹1750/side)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Ambernath East</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>hinglish</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Inquiry</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:23:10.359424</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29T00:31:28.211320</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1573,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28T22:59:17.913900</t>
+          <t>2026-10-29T01:23:10.368454</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -1565,7 +1614,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T22:59:17.914950</t>
+          <t>2026-10-29T01:23:10.369530</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1606,7 +1655,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28T22:59:17.914990</t>
+          <t>2026-10-29T01:23:10.369579</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -1647,7 +1696,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T22:59:17.914998</t>
+          <t>2026-10-29T01:23:10.369588</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1688,7 +1737,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28T22:59:17.915004</t>
+          <t>2026-10-29T01:23:10.369596</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1729,7 +1778,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T22:59:17.915009</t>
+          <t>2026-10-29T01:23:10.369604</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1770,7 +1819,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28T22:59:17.915018</t>
+          <t>2026-10-29T01:23:10.369616</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1811,7 +1860,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28T22:59:17.915023</t>
+          <t>2026-10-29T01:23:10.369623</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1842,7 +1891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3305,7 +3354,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -3342,7 +3391,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -3379,7 +3428,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -3416,7 +3465,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -3453,7 +3502,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -3490,7 +3539,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -3527,7 +3576,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -3564,7 +3613,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -3601,7 +3650,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -3638,7 +3687,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -3675,7 +3724,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -3712,7 +3761,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -3749,7 +3798,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -3786,7 +3835,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -3823,7 +3872,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -3860,7 +3909,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -3897,7 +3946,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -3934,7 +3983,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -4008,7 +4057,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -4045,7 +4094,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -4082,7 +4131,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -4119,7 +4168,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -4156,7 +4205,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -4193,7 +4242,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -4230,7 +4279,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -4267,7 +4316,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -4378,7 +4427,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -4415,7 +4464,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -4452,7 +4501,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -4489,7 +4538,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -4526,7 +4575,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -4559,7 +4608,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -4596,7 +4645,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -4633,7 +4682,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -4744,7 +4793,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -4781,7 +4830,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -4818,7 +4867,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -4855,7 +4904,7 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -4892,7 +4941,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -4929,7 +4978,7 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -4966,7 +5015,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -5003,7 +5052,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -5040,7 +5089,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -5077,7 +5126,7 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -5110,7 +5159,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -5143,7 +5192,7 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -5180,7 +5229,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -5217,7 +5266,7 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
@@ -5254,7 +5303,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -5265,6 +5314,117 @@
       <c r="G94" s="2" t="inlineStr">
         <is>
           <t>2026-10-28T22:59:17.923381</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="22" customHeight="1">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1793210288296</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 28 Oct]</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28T23:28:10.191584</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="22" customHeight="1">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1793214187903</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 29 Oct]</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29T00:33:09.820916</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="22" customHeight="1">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>aipost_1793217093025</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 29 Oct]</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29T01:21:34.839230</t>
         </is>
       </c>
     </row>

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T01:23:10.360759</t>
+          <t>2026-10-30T00:47:46.830099</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T01:23:10.360767</t>
+          <t>2026-10-30T00:47:46.830109</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T01:23:10.360774</t>
+          <t>2026-10-30T00:47:46.830116</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T01:23:10.360751</t>
+          <t>2026-10-30T00:47:46.830089</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T01:23:10.360743</t>
+          <t>2026-10-30T00:47:46.830081</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T01:23:10.360734</t>
+          <t>2026-10-30T00:47:46.830072</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1281,7 +1281,7 @@
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T01:23:10.360724</t>
+          <t>2026-10-30T00:47:46.830062</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       <c r="I11" s="4" t="inlineStr"/>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T01:23:10.360687</t>
+          <t>2026-10-30T00:47:46.829998</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -1428,7 +1428,7 @@
       <c r="I13" s="4" t="inlineStr"/>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T01:23:10.359424</t>
+          <t>2026-10-30T00:47:46.828244</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T01:23:10.368454</t>
+          <t>2026-10-30T00:47:46.931635</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T01:23:10.369530</t>
+          <t>2026-10-30T00:47:46.933897</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T01:23:10.369579</t>
+          <t>2026-10-30T00:47:46.933943</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T01:23:10.369588</t>
+          <t>2026-10-30T00:47:46.933950</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T01:23:10.369596</t>
+          <t>2026-10-30T00:47:46.933955</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T01:23:10.369604</t>
+          <t>2026-10-30T00:47:46.933961</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29T01:23:10.369616</t>
+          <t>2026-10-30T00:47:46.933972</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29T01:23:10.369623</t>
+          <t>2026-10-30T00:47:46.933977</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -4057,7 +4057,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -4427,7 +4427,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
@@ -5425,6 +5425,43 @@
       <c r="G97" s="4" t="inlineStr">
         <is>
           <t>2026-10-29T01:21:34.839230</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="22" customHeight="1">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>aipost_1793300419006</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Official Registered Rent Agreement at ₹1,750 (Doorstep Biometric) [AI Verified: 30 Oct]</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Need Govt Registered Rent Agreement in Ambernath, Badlapur, Ulhasnagar or Kalyan? Dashmesh Properties provides 100% legal e-registration with doorstep biometric verification for just ₹1,750 per side (₹3,500 all-inclusive with stamp duty &amp; registration). Instant slot booking!</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Book Doorstep Biometric (+91 84210 77613)</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Published (AI Autonomous)</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-30T00:30:21.174733</t>
         </is>
       </c>
     </row>

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T00:47:46.830099</t>
+          <t>2026-10-30T01:29:59.410473</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:47:46.830109</t>
+          <t>2026-10-30T01:29:59.410478</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T00:47:46.830116</t>
+          <t>2026-10-30T01:29:59.410483</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:47:46.830089</t>
+          <t>2026-10-30T01:29:59.410468</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T00:47:46.830081</t>
+          <t>2026-10-30T01:29:59.410462</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:47:46.830072</t>
+          <t>2026-10-30T01:29:59.410457</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1281,7 +1281,7 @@
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T00:47:46.830062</t>
+          <t>2026-10-30T01:29:59.410450</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       <c r="I11" s="4" t="inlineStr"/>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:47:46.829998</t>
+          <t>2026-10-30T01:29:59.410423</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -1428,7 +1428,7 @@
       <c r="I13" s="4" t="inlineStr"/>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:47:46.828244</t>
+          <t>2026-10-30T01:29:59.409430</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:47:46.931635</t>
+          <t>2026-10-30T01:29:59.417302</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T00:47:46.933897</t>
+          <t>2026-10-30T01:29:59.418197</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:47:46.933943</t>
+          <t>2026-10-30T01:29:59.418221</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T00:47:46.933950</t>
+          <t>2026-10-30T01:29:59.418227</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:47:46.933955</t>
+          <t>2026-10-30T01:29:59.418232</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T00:47:46.933961</t>
+          <t>2026-10-30T01:29:59.418237</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T00:47:46.933972</t>
+          <t>2026-10-30T01:29:59.418244</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T00:47:46.933977</t>
+          <t>2026-10-30T01:29:59.418249</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">

--- a/data/Dashmesh_Master_Database.xlsx
+++ b/data/Dashmesh_Master_Database.xlsx
@@ -889,7 +889,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T01:29:59.410473</t>
+          <t>2026-10-30T01:44:02.222375</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       <c r="I3" s="4" t="inlineStr"/>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T01:29:59.410478</t>
+          <t>2026-10-30T01:44:02.222380</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       <c r="I4" s="2" t="inlineStr"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T01:29:59.410483</t>
+          <t>2026-10-30T01:44:02.222385</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       <c r="I5" s="4" t="inlineStr"/>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T01:29:59.410468</t>
+          <t>2026-10-30T01:44:02.222370</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       <c r="I6" s="2" t="inlineStr"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T01:29:59.410462</t>
+          <t>2026-10-30T01:44:02.222365</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       <c r="I7" s="4" t="inlineStr"/>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T01:29:59.410457</t>
+          <t>2026-10-30T01:44:02.222360</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -1281,7 +1281,7 @@
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T01:29:59.410450</t>
+          <t>2026-10-30T01:44:02.222354</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1330,7 +1330,7 @@
       <c r="I11" s="4" t="inlineStr"/>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T01:29:59.410423</t>
+          <t>2026-10-30T01:44:02.222320</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -1428,7 +1428,7 @@
       <c r="I13" s="4" t="inlineStr"/>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T01:29:59.409430</t>
+          <t>2026-10-30T01:44:02.221370</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T01:29:59.417302</t>
+          <t>2026-10-30T01:44:02.246216</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T01:29:59.418197</t>
+          <t>2026-10-30T01:44:02.246917</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T01:29:59.418221</t>
+          <t>2026-10-30T01:44:02.246936</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T01:29:59.418227</t>
+          <t>2026-10-30T01:44:02.246942</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T01:29:59.418232</t>
+          <t>2026-10-30T01:44:02.246947</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T01:29:59.418237</t>
+          <t>2026-10-30T01:44:02.246951</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-30T01:29:59.418244</t>
+          <t>2026-10-30T01:44:02.246958</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-30T01:29:59.418249</t>
+          <t>2026-10-30T01:44:02.246962</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
